--- a/documents_bin/1818图册目录模板.xlsx
+++ b/documents_bin/1818图册目录模板.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project\auto-fanban-pre\documents_bin\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93861D3-CDBD-4E65-A698-2BB6EA098DB5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,9 +28,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -291,14 +297,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -320,157 +320,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -500,8 +349,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,198 +364,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="45"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -867,261 +535,19 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="60">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -1137,13 +563,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1159,7 +585,70 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="53" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1168,193 +657,107 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="55" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="60">
+  <cellStyles count="12">
+    <cellStyle name="差_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="差_Sheet1" xfId="49"/>
-    <cellStyle name="常规 10" xfId="50"/>
-    <cellStyle name="常规 10 10" xfId="51"/>
-    <cellStyle name="常规 15 49" xfId="52"/>
-    <cellStyle name="常规 2" xfId="53"/>
-    <cellStyle name="常规 20" xfId="54"/>
-    <cellStyle name="常规 4" xfId="55"/>
-    <cellStyle name="常规 7 12" xfId="56"/>
-    <cellStyle name="常规 9 10" xfId="57"/>
-    <cellStyle name="超链接 2" xfId="58"/>
-    <cellStyle name="超链接 3" xfId="59"/>
+    <cellStyle name="常规 10" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 10 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 15 49" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="常规 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="常规 20" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="常规 4" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="常规 7 12" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="常规 9 10" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="超链接 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="超链接 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1641,14 +1044,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I150"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB150"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
@@ -1663,272 +1066,327 @@
     <col min="11" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:9">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" spans="1:9">
-      <c r="A2" s="13" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="50"/>
+    </row>
+    <row r="2" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="16" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1" spans="1:9">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="21" t="s">
+      <c r="G2" s="31"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="52"/>
+    </row>
+    <row r="3" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="4" t="s">
+      <c r="G3" s="32"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="52"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.15">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="21" t="s">
+      <c r="E4" s="33"/>
+      <c r="F4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:9">
-      <c r="A5" s="13" t="s">
+      <c r="G4" s="32"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
+    </row>
+    <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="16" t="s">
+      <c r="E5" s="33"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="26"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="27" t="s">
+      <c r="H5" s="43"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.15">
+      <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="30" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="31"/>
-      <c r="I6" s="32"/>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="14.25" customHeight="1" spans="1:9">
-      <c r="A7" s="33" t="s">
+      <c r="H6" s="44"/>
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:28" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="46"/>
+      <c r="D7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="38" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="36"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-    </row>
-    <row r="9" ht="69.95" customHeight="1" spans="1:9">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.15">
+      <c r="A8" s="39"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+    </row>
+    <row r="9" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="46"/>
-    </row>
-    <row r="10" ht="69.95" customHeight="1" spans="1:9">
+      <c r="B9" s="36"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="46"/>
-    </row>
-    <row r="11" ht="69.95" customHeight="1" spans="1:9">
+      <c r="B10" s="36"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="46"/>
-    </row>
-    <row r="12" ht="69.95" customHeight="1" spans="1:9">
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="46"/>
-    </row>
-    <row r="13" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A13" s="47"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-    </row>
-    <row r="14" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A14" s="47"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-    </row>
-    <row r="15" s="5" customFormat="1" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A15" s="47"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-    </row>
-    <row r="16" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A16" s="47"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-    </row>
-    <row r="17" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A17" s="47"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-    </row>
-    <row r="18" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A18" s="47"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-    </row>
-    <row r="19" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A19" s="47"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-    </row>
-    <row r="20" ht="69.95" customHeight="1" spans="1:9">
-      <c r="A20" s="47"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-    </row>
-    <row r="21" ht="69.95" customHeight="1" spans="1:9">
+      <c r="B12" s="36"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="25"/>
+    </row>
+    <row r="13" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="26"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+    </row>
+    <row r="14" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="26"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="53"/>
+      <c r="W14" s="53"/>
+      <c r="X14" s="53"/>
+      <c r="Y14" s="53"/>
+      <c r="Z14" s="53"/>
+      <c r="AA14" s="53"/>
+      <c r="AB14" s="53"/>
+    </row>
+    <row r="15" spans="1:28" s="5" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="26"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="54"/>
+      <c r="V15" s="54"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54"/>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="54"/>
+    </row>
+    <row r="16" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="26"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="53"/>
+      <c r="U16" s="53"/>
+      <c r="V16" s="53"/>
+      <c r="W16" s="53"/>
+      <c r="X16" s="53"/>
+      <c r="Y16" s="53"/>
+      <c r="Z16" s="53"/>
+      <c r="AA16" s="53"/>
+      <c r="AB16" s="53"/>
+    </row>
+    <row r="17" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="26"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+    </row>
+    <row r="18" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="26"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+    </row>
+    <row r="19" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="26"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+    </row>
+    <row r="20" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="26"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+    </row>
+    <row r="21" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="42"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="37"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -1936,10 +1394,10 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" ht="69.95" customHeight="1" spans="1:9">
+    <row r="22" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="42"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -1947,10 +1405,10 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" ht="69.95" customHeight="1" spans="1:9">
+    <row r="23" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="37"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -1958,10 +1416,10 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" ht="69.95" customHeight="1" spans="1:9">
+    <row r="24" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="42"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1969,10 +1427,10 @@
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" ht="69.95" customHeight="1" spans="1:9">
+    <row r="25" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="42"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="37"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -1980,10 +1438,10 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" ht="69.95" customHeight="1" spans="1:9">
+    <row r="26" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="42"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1991,10 +1449,10 @@
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" ht="69.95" customHeight="1" spans="1:9">
+    <row r="27" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="42"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2002,10 +1460,10 @@
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" ht="69.95" customHeight="1" spans="1:9">
+    <row r="28" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="42"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="37"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -2013,10 +1471,10 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" ht="69.95" customHeight="1" spans="1:9">
+    <row r="29" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="42"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -2024,10 +1482,10 @@
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" ht="69.95" customHeight="1" spans="1:9">
+    <row r="30" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="42"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -2035,10 +1493,10 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
-    <row r="31" ht="69.95" customHeight="1" spans="1:9">
+    <row r="31" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="42"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -2046,10 +1504,10 @@
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" ht="69.95" customHeight="1" spans="1:9">
+    <row r="32" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="42"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="37"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -2057,10 +1515,10 @@
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
-    <row r="33" ht="69.95" customHeight="1" spans="1:9">
+    <row r="33" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="42"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -2068,10 +1526,10 @@
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
     </row>
-    <row r="34" ht="69.95" customHeight="1" spans="1:9">
+    <row r="34" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="42"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="37"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -2079,10 +1537,10 @@
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
-    <row r="35" ht="69.95" customHeight="1" spans="1:9">
+    <row r="35" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="42"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -2090,10 +1548,10 @@
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
     </row>
-    <row r="36" ht="69.95" customHeight="1" spans="1:9">
+    <row r="36" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="42"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -2101,10 +1559,10 @@
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
-    <row r="37" ht="69.95" customHeight="1" spans="1:9">
+    <row r="37" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="42"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="37"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -2112,10 +1570,10 @@
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
     </row>
-    <row r="38" ht="69.95" customHeight="1" spans="1:9">
+    <row r="38" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="42"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="37"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -2123,10 +1581,10 @@
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
     </row>
-    <row r="39" ht="69.95" customHeight="1" spans="1:9">
+    <row r="39" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="42"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="37"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -2134,10 +1592,10 @@
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
     </row>
-    <row r="40" ht="69.95" customHeight="1" spans="1:9">
+    <row r="40" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="42"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="37"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -2145,10 +1603,10 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
-    <row r="41" ht="69.95" customHeight="1" spans="1:9">
+    <row r="41" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="42"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="37"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -2156,10 +1614,10 @@
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
     </row>
-    <row r="42" ht="69.95" customHeight="1" spans="1:9">
+    <row r="42" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="42"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="37"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -2167,10 +1625,10 @@
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
     </row>
-    <row r="43" ht="69.95" customHeight="1" spans="1:9">
+    <row r="43" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="5"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="42"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -2178,10 +1636,10 @@
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
     </row>
-    <row r="44" ht="69.95" customHeight="1" spans="1:9">
+    <row r="44" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="42"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="37"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -2189,10 +1647,10 @@
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
     </row>
-    <row r="45" ht="69.95" customHeight="1" spans="1:9">
+    <row r="45" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="42"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="37"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -2200,10 +1658,10 @@
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
     </row>
-    <row r="46" ht="69.95" customHeight="1" spans="1:9">
+    <row r="46" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="42"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="37"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -2211,10 +1669,10 @@
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
     </row>
-    <row r="47" ht="69.95" customHeight="1" spans="1:9">
+    <row r="47" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="5"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="42"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="37"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -2222,10 +1680,10 @@
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
     </row>
-    <row r="48" ht="69.95" customHeight="1" spans="1:9">
+    <row r="48" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="5"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="42"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="37"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -2233,10 +1691,10 @@
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
     </row>
-    <row r="49" ht="69.95" customHeight="1" spans="1:9">
+    <row r="49" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="5"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="42"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="37"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -2244,10 +1702,10 @@
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
     </row>
-    <row r="50" ht="69.95" customHeight="1" spans="1:9">
+    <row r="50" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="5"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="42"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="37"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -2255,10 +1713,10 @@
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
     </row>
-    <row r="51" ht="69.95" customHeight="1" spans="1:9">
+    <row r="51" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="42"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="37"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
@@ -2266,10 +1724,10 @@
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
     </row>
-    <row r="52" ht="69.95" customHeight="1" spans="1:9">
+    <row r="52" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="5"/>
-      <c r="B52" s="41"/>
-      <c r="C52" s="42"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="37"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
@@ -2277,10 +1735,10 @@
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
     </row>
-    <row r="53" ht="69.95" customHeight="1" spans="1:9">
+    <row r="53" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="42"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="37"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
@@ -2288,10 +1746,10 @@
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
     </row>
-    <row r="54" ht="69.95" customHeight="1" spans="1:9">
+    <row r="54" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="5"/>
-      <c r="B54" s="41"/>
-      <c r="C54" s="42"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
@@ -2299,10 +1757,10 @@
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
     </row>
-    <row r="55" ht="69.95" customHeight="1" spans="1:9">
+    <row r="55" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="5"/>
-      <c r="B55" s="41"/>
-      <c r="C55" s="42"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
@@ -2310,10 +1768,10 @@
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
     </row>
-    <row r="56" ht="69.95" customHeight="1" spans="1:9">
+    <row r="56" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="5"/>
-      <c r="B56" s="41"/>
-      <c r="C56" s="42"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="37"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -2321,10 +1779,10 @@
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
-    <row r="57" ht="69.95" customHeight="1" spans="1:9">
+    <row r="57" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="5"/>
-      <c r="B57" s="41"/>
-      <c r="C57" s="42"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="37"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -2332,10 +1790,10 @@
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
     </row>
-    <row r="58" ht="69.95" customHeight="1" spans="1:9">
+    <row r="58" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="5"/>
-      <c r="B58" s="41"/>
-      <c r="C58" s="42"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="37"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
@@ -2343,10 +1801,10 @@
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
     </row>
-    <row r="59" ht="69.95" customHeight="1" spans="1:9">
+    <row r="59" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="5"/>
-      <c r="B59" s="41"/>
-      <c r="C59" s="42"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="37"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
@@ -2354,10 +1812,10 @@
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
-    <row r="60" ht="69.95" customHeight="1" spans="1:9">
+    <row r="60" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="5"/>
-      <c r="B60" s="41"/>
-      <c r="C60" s="42"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="37"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
@@ -2365,10 +1823,10 @@
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" ht="69.95" customHeight="1" spans="1:9">
+    <row r="61" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="5"/>
-      <c r="B61" s="41"/>
-      <c r="C61" s="42"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="37"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
@@ -2376,10 +1834,10 @@
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
     </row>
-    <row r="62" ht="69.95" customHeight="1" spans="1:9">
+    <row r="62" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="5"/>
-      <c r="B62" s="41"/>
-      <c r="C62" s="42"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="37"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
@@ -2387,10 +1845,10 @@
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
     </row>
-    <row r="63" ht="69.95" customHeight="1" spans="1:9">
+    <row r="63" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="5"/>
-      <c r="B63" s="41"/>
-      <c r="C63" s="42"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="37"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
@@ -2398,10 +1856,10 @@
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
     </row>
-    <row r="64" ht="69.95" customHeight="1" spans="1:9">
+    <row r="64" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="5"/>
-      <c r="B64" s="41"/>
-      <c r="C64" s="42"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="37"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
@@ -2409,10 +1867,10 @@
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
     </row>
-    <row r="65" ht="69.95" customHeight="1" spans="1:9">
+    <row r="65" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="5"/>
-      <c r="B65" s="41"/>
-      <c r="C65" s="42"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="37"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
@@ -2420,10 +1878,10 @@
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
     </row>
-    <row r="66" ht="69.95" customHeight="1" spans="1:9">
+    <row r="66" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="5"/>
-      <c r="B66" s="41"/>
-      <c r="C66" s="42"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="37"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
@@ -2431,10 +1889,10 @@
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
     </row>
-    <row r="67" ht="69.95" customHeight="1" spans="1:9">
+    <row r="67" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="5"/>
-      <c r="B67" s="41"/>
-      <c r="C67" s="42"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="37"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
@@ -2442,10 +1900,10 @@
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
     </row>
-    <row r="68" ht="69.95" customHeight="1" spans="1:9">
+    <row r="68" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="5"/>
-      <c r="B68" s="41"/>
-      <c r="C68" s="42"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="37"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
@@ -2453,10 +1911,10 @@
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
     </row>
-    <row r="69" ht="69.95" customHeight="1" spans="1:9">
+    <row r="69" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="5"/>
-      <c r="B69" s="41"/>
-      <c r="C69" s="42"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="37"/>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
@@ -2464,10 +1922,10 @@
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
     </row>
-    <row r="70" ht="69.95" customHeight="1" spans="1:9">
+    <row r="70" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="5"/>
-      <c r="B70" s="41"/>
-      <c r="C70" s="42"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="37"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
@@ -2475,10 +1933,10 @@
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
     </row>
-    <row r="71" ht="69.95" customHeight="1" spans="1:9">
+    <row r="71" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="5"/>
-      <c r="B71" s="41"/>
-      <c r="C71" s="42"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="37"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
@@ -2486,10 +1944,10 @@
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
     </row>
-    <row r="72" ht="69.95" customHeight="1" spans="1:9">
+    <row r="72" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="5"/>
-      <c r="B72" s="41"/>
-      <c r="C72" s="42"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="37"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
@@ -2497,10 +1955,10 @@
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
     </row>
-    <row r="73" ht="69.95" customHeight="1" spans="1:9">
+    <row r="73" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="5"/>
-      <c r="B73" s="41"/>
-      <c r="C73" s="42"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="37"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
@@ -2508,10 +1966,10 @@
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
     </row>
-    <row r="74" ht="69.95" customHeight="1" spans="1:9">
+    <row r="74" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="5"/>
-      <c r="B74" s="41"/>
-      <c r="C74" s="42"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="37"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
@@ -2519,10 +1977,10 @@
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
     </row>
-    <row r="75" ht="69.95" customHeight="1" spans="1:9">
+    <row r="75" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="5"/>
-      <c r="B75" s="41"/>
-      <c r="C75" s="42"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="37"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
@@ -2530,10 +1988,10 @@
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
     </row>
-    <row r="76" ht="69.95" customHeight="1" spans="1:9">
+    <row r="76" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="5"/>
-      <c r="B76" s="41"/>
-      <c r="C76" s="42"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="37"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
@@ -2541,10 +1999,10 @@
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
     </row>
-    <row r="77" ht="69.95" customHeight="1" spans="1:9">
+    <row r="77" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="5"/>
-      <c r="B77" s="41"/>
-      <c r="C77" s="42"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="37"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
@@ -2552,10 +2010,10 @@
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
     </row>
-    <row r="78" ht="69.95" customHeight="1" spans="1:9">
+    <row r="78" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="5"/>
-      <c r="B78" s="41"/>
-      <c r="C78" s="42"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="37"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
@@ -2563,10 +2021,10 @@
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
     </row>
-    <row r="79" ht="69.95" customHeight="1" spans="1:9">
+    <row r="79" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="5"/>
-      <c r="B79" s="41"/>
-      <c r="C79" s="42"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="37"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
@@ -2574,10 +2032,10 @@
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
     </row>
-    <row r="80" ht="69.95" customHeight="1" spans="1:9">
+    <row r="80" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="5"/>
-      <c r="B80" s="41"/>
-      <c r="C80" s="42"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="37"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
@@ -2585,10 +2043,10 @@
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
     </row>
-    <row r="81" ht="69.95" customHeight="1" spans="1:9">
+    <row r="81" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="5"/>
-      <c r="B81" s="41"/>
-      <c r="C81" s="42"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="37"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
@@ -2596,10 +2054,10 @@
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
     </row>
-    <row r="82" ht="69.95" customHeight="1" spans="1:9">
+    <row r="82" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="5"/>
-      <c r="B82" s="41"/>
-      <c r="C82" s="42"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="37"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
@@ -2607,10 +2065,10 @@
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
     </row>
-    <row r="83" ht="69.95" customHeight="1" spans="1:9">
+    <row r="83" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="5"/>
-      <c r="B83" s="41"/>
-      <c r="C83" s="42"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="37"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
@@ -2618,10 +2076,10 @@
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
     </row>
-    <row r="84" ht="69.95" customHeight="1" spans="1:9">
+    <row r="84" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="5"/>
-      <c r="B84" s="41"/>
-      <c r="C84" s="42"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="37"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
@@ -2629,10 +2087,10 @@
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
     </row>
-    <row r="85" ht="69.95" customHeight="1" spans="1:9">
+    <row r="85" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="5"/>
-      <c r="B85" s="41"/>
-      <c r="C85" s="42"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
@@ -2640,10 +2098,10 @@
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
     </row>
-    <row r="86" ht="69.95" customHeight="1" spans="1:9">
+    <row r="86" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="5"/>
-      <c r="B86" s="41"/>
-      <c r="C86" s="42"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="37"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
@@ -2651,10 +2109,10 @@
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
     </row>
-    <row r="87" ht="69.95" customHeight="1" spans="1:9">
+    <row r="87" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="5"/>
-      <c r="B87" s="41"/>
-      <c r="C87" s="42"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="37"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
@@ -2662,10 +2120,10 @@
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
     </row>
-    <row r="88" ht="69.95" customHeight="1" spans="1:9">
+    <row r="88" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="5"/>
-      <c r="B88" s="41"/>
-      <c r="C88" s="42"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="37"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
@@ -2673,10 +2131,10 @@
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
     </row>
-    <row r="89" ht="69.95" customHeight="1" spans="1:9">
+    <row r="89" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="5"/>
-      <c r="B89" s="41"/>
-      <c r="C89" s="42"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="37"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
@@ -2684,10 +2142,10 @@
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
     </row>
-    <row r="90" ht="69.95" customHeight="1" spans="1:9">
+    <row r="90" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="5"/>
-      <c r="B90" s="41"/>
-      <c r="C90" s="42"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="37"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
@@ -2695,10 +2153,10 @@
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
     </row>
-    <row r="91" ht="69.95" customHeight="1" spans="1:9">
+    <row r="91" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="5"/>
-      <c r="B91" s="41"/>
-      <c r="C91" s="42"/>
+      <c r="B91" s="36"/>
+      <c r="C91" s="37"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
@@ -2706,10 +2164,10 @@
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
     </row>
-    <row r="92" ht="69.95" customHeight="1" spans="1:9">
+    <row r="92" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="5"/>
-      <c r="B92" s="41"/>
-      <c r="C92" s="42"/>
+      <c r="B92" s="36"/>
+      <c r="C92" s="37"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
@@ -2717,10 +2175,10 @@
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
     </row>
-    <row r="93" ht="69.95" customHeight="1" spans="1:9">
+    <row r="93" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="5"/>
-      <c r="B93" s="41"/>
-      <c r="C93" s="42"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="37"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
@@ -2728,10 +2186,10 @@
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
     </row>
-    <row r="94" ht="69.95" customHeight="1" spans="1:9">
+    <row r="94" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="5"/>
-      <c r="B94" s="41"/>
-      <c r="C94" s="42"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
@@ -2739,10 +2197,10 @@
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
     </row>
-    <row r="95" ht="69.95" customHeight="1" spans="1:9">
+    <row r="95" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="5"/>
-      <c r="B95" s="41"/>
-      <c r="C95" s="42"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="37"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
@@ -2750,10 +2208,10 @@
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
     </row>
-    <row r="96" ht="69.95" customHeight="1" spans="1:9">
+    <row r="96" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="5"/>
-      <c r="B96" s="41"/>
-      <c r="C96" s="42"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="37"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
@@ -2761,10 +2219,10 @@
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
     </row>
-    <row r="97" ht="69.95" customHeight="1" spans="1:9">
+    <row r="97" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="5"/>
-      <c r="B97" s="41"/>
-      <c r="C97" s="42"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="37"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
@@ -2772,10 +2230,10 @@
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
     </row>
-    <row r="98" ht="69.95" customHeight="1" spans="1:9">
+    <row r="98" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="5"/>
-      <c r="B98" s="41"/>
-      <c r="C98" s="42"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="37"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
@@ -2783,10 +2241,10 @@
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
     </row>
-    <row r="99" ht="69.95" customHeight="1" spans="1:9">
+    <row r="99" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="5"/>
-      <c r="B99" s="41"/>
-      <c r="C99" s="42"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="37"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
@@ -2794,10 +2252,10 @@
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
     </row>
-    <row r="100" ht="69.95" customHeight="1" spans="1:9">
+    <row r="100" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="5"/>
-      <c r="B100" s="41"/>
-      <c r="C100" s="42"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="37"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
@@ -2805,10 +2263,10 @@
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
     </row>
-    <row r="101" ht="69.95" customHeight="1" spans="1:9">
+    <row r="101" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="5"/>
-      <c r="B101" s="41"/>
-      <c r="C101" s="42"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="37"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
@@ -2816,10 +2274,10 @@
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
     </row>
-    <row r="102" ht="69.95" customHeight="1" spans="1:9">
+    <row r="102" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="5"/>
-      <c r="B102" s="41"/>
-      <c r="C102" s="42"/>
+      <c r="B102" s="36"/>
+      <c r="C102" s="37"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
@@ -2827,10 +2285,10 @@
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
     </row>
-    <row r="103" ht="69.95" customHeight="1" spans="1:9">
+    <row r="103" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="5"/>
-      <c r="B103" s="41"/>
-      <c r="C103" s="42"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="37"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
@@ -2838,10 +2296,10 @@
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
     </row>
-    <row r="104" ht="69.95" customHeight="1" spans="1:9">
+    <row r="104" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="5"/>
-      <c r="B104" s="41"/>
-      <c r="C104" s="42"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="37"/>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
@@ -2849,10 +2307,10 @@
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
     </row>
-    <row r="105" ht="69.95" customHeight="1" spans="1:9">
+    <row r="105" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="5"/>
-      <c r="B105" s="41"/>
-      <c r="C105" s="42"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="37"/>
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
@@ -2860,10 +2318,10 @@
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
     </row>
-    <row r="106" ht="69.95" customHeight="1" spans="1:9">
+    <row r="106" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="5"/>
-      <c r="B106" s="41"/>
-      <c r="C106" s="42"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="37"/>
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
@@ -2871,10 +2329,10 @@
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
     </row>
-    <row r="107" ht="69.95" customHeight="1" spans="1:9">
+    <row r="107" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="5"/>
-      <c r="B107" s="41"/>
-      <c r="C107" s="42"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="37"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
@@ -2882,10 +2340,10 @@
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
     </row>
-    <row r="108" ht="69.95" customHeight="1" spans="1:9">
+    <row r="108" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="5"/>
-      <c r="B108" s="41"/>
-      <c r="C108" s="42"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="37"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
@@ -2893,10 +2351,10 @@
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
     </row>
-    <row r="109" ht="69.95" customHeight="1" spans="1:9">
+    <row r="109" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="5"/>
-      <c r="B109" s="41"/>
-      <c r="C109" s="42"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="37"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
@@ -2904,10 +2362,10 @@
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
     </row>
-    <row r="110" ht="69.95" customHeight="1" spans="1:9">
+    <row r="110" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="5"/>
-      <c r="B110" s="41"/>
-      <c r="C110" s="42"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="37"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
@@ -2915,10 +2373,10 @@
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
     </row>
-    <row r="111" ht="69.95" customHeight="1" spans="1:9">
+    <row r="111" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="5"/>
-      <c r="B111" s="41"/>
-      <c r="C111" s="42"/>
+      <c r="B111" s="36"/>
+      <c r="C111" s="37"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
@@ -2926,10 +2384,10 @@
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
     </row>
-    <row r="112" ht="69.95" customHeight="1" spans="1:9">
+    <row r="112" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="5"/>
-      <c r="B112" s="41"/>
-      <c r="C112" s="42"/>
+      <c r="B112" s="36"/>
+      <c r="C112" s="37"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
@@ -2937,10 +2395,10 @@
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
     </row>
-    <row r="113" ht="69.95" customHeight="1" spans="1:9">
+    <row r="113" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="5"/>
-      <c r="B113" s="41"/>
-      <c r="C113" s="42"/>
+      <c r="B113" s="36"/>
+      <c r="C113" s="37"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
@@ -2948,10 +2406,10 @@
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
     </row>
-    <row r="114" ht="69.95" customHeight="1" spans="1:9">
+    <row r="114" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="5"/>
-      <c r="B114" s="41"/>
-      <c r="C114" s="42"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="37"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
@@ -2959,10 +2417,10 @@
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
     </row>
-    <row r="115" ht="69.95" customHeight="1" spans="1:9">
+    <row r="115" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5"/>
-      <c r="B115" s="41"/>
-      <c r="C115" s="42"/>
+      <c r="B115" s="36"/>
+      <c r="C115" s="37"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
@@ -2970,10 +2428,10 @@
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
     </row>
-    <row r="116" ht="69.95" customHeight="1" spans="1:9">
+    <row r="116" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5"/>
-      <c r="B116" s="41"/>
-      <c r="C116" s="42"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="37"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -2981,10 +2439,10 @@
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
     </row>
-    <row r="117" ht="69.95" customHeight="1" spans="1:9">
+    <row r="117" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="5"/>
-      <c r="B117" s="41"/>
-      <c r="C117" s="42"/>
+      <c r="B117" s="36"/>
+      <c r="C117" s="37"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -2992,10 +2450,10 @@
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
     </row>
-    <row r="118" ht="69.95" customHeight="1" spans="1:9">
+    <row r="118" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="5"/>
-      <c r="B118" s="41"/>
-      <c r="C118" s="42"/>
+      <c r="B118" s="36"/>
+      <c r="C118" s="37"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -3003,10 +2461,10 @@
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
     </row>
-    <row r="119" ht="69.95" customHeight="1" spans="1:9">
+    <row r="119" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="5"/>
-      <c r="B119" s="41"/>
-      <c r="C119" s="42"/>
+      <c r="B119" s="36"/>
+      <c r="C119" s="37"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -3014,10 +2472,10 @@
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
     </row>
-    <row r="120" ht="69.95" customHeight="1" spans="1:9">
+    <row r="120" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="5"/>
-      <c r="B120" s="41"/>
-      <c r="C120" s="42"/>
+      <c r="B120" s="36"/>
+      <c r="C120" s="37"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -3025,10 +2483,10 @@
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
     </row>
-    <row r="121" ht="69.95" customHeight="1" spans="1:9">
+    <row r="121" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="5"/>
-      <c r="B121" s="41"/>
-      <c r="C121" s="42"/>
+      <c r="B121" s="36"/>
+      <c r="C121" s="37"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -3036,10 +2494,10 @@
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
     </row>
-    <row r="122" ht="69.95" customHeight="1" spans="1:9">
+    <row r="122" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="5"/>
-      <c r="B122" s="41"/>
-      <c r="C122" s="42"/>
+      <c r="B122" s="36"/>
+      <c r="C122" s="37"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -3047,10 +2505,10 @@
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
     </row>
-    <row r="123" ht="69.95" customHeight="1" spans="1:9">
+    <row r="123" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="5"/>
-      <c r="B123" s="41"/>
-      <c r="C123" s="42"/>
+      <c r="B123" s="36"/>
+      <c r="C123" s="37"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -3058,10 +2516,10 @@
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
     </row>
-    <row r="124" ht="69.95" customHeight="1" spans="1:9">
+    <row r="124" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5"/>
-      <c r="B124" s="41"/>
-      <c r="C124" s="42"/>
+      <c r="B124" s="36"/>
+      <c r="C124" s="37"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -3069,10 +2527,10 @@
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
     </row>
-    <row r="125" ht="69.95" customHeight="1" spans="1:9">
+    <row r="125" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5"/>
-      <c r="B125" s="41"/>
-      <c r="C125" s="42"/>
+      <c r="B125" s="36"/>
+      <c r="C125" s="37"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -3080,10 +2538,10 @@
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
     </row>
-    <row r="126" ht="69.95" customHeight="1" spans="1:9">
+    <row r="126" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5"/>
-      <c r="B126" s="41"/>
-      <c r="C126" s="42"/>
+      <c r="B126" s="36"/>
+      <c r="C126" s="37"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -3091,10 +2549,10 @@
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
     </row>
-    <row r="127" ht="69.95" customHeight="1" spans="1:9">
+    <row r="127" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5"/>
-      <c r="B127" s="41"/>
-      <c r="C127" s="42"/>
+      <c r="B127" s="36"/>
+      <c r="C127" s="37"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -3102,10 +2560,10 @@
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
     </row>
-    <row r="128" ht="69.95" customHeight="1" spans="1:9">
+    <row r="128" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5"/>
-      <c r="B128" s="41"/>
-      <c r="C128" s="42"/>
+      <c r="B128" s="36"/>
+      <c r="C128" s="37"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -3113,10 +2571,10 @@
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
     </row>
-    <row r="129" ht="69.95" customHeight="1" spans="1:9">
+    <row r="129" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="5"/>
-      <c r="B129" s="41"/>
-      <c r="C129" s="42"/>
+      <c r="B129" s="36"/>
+      <c r="C129" s="37"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -3124,10 +2582,10 @@
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
     </row>
-    <row r="130" ht="69.95" customHeight="1" spans="1:9">
+    <row r="130" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="5"/>
-      <c r="B130" s="41"/>
-      <c r="C130" s="42"/>
+      <c r="B130" s="36"/>
+      <c r="C130" s="37"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -3135,10 +2593,10 @@
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
     </row>
-    <row r="131" ht="69.95" customHeight="1" spans="1:9">
+    <row r="131" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="5"/>
-      <c r="B131" s="41"/>
-      <c r="C131" s="42"/>
+      <c r="B131" s="36"/>
+      <c r="C131" s="37"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -3146,10 +2604,10 @@
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
     </row>
-    <row r="132" ht="69.95" customHeight="1" spans="1:9">
+    <row r="132" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="5"/>
-      <c r="B132" s="41"/>
-      <c r="C132" s="42"/>
+      <c r="B132" s="36"/>
+      <c r="C132" s="37"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -3157,10 +2615,10 @@
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
     </row>
-    <row r="133" ht="69.95" customHeight="1" spans="1:9">
+    <row r="133" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5"/>
-      <c r="B133" s="41"/>
-      <c r="C133" s="42"/>
+      <c r="B133" s="36"/>
+      <c r="C133" s="37"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -3168,10 +2626,10 @@
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
     </row>
-    <row r="134" ht="69.95" customHeight="1" spans="1:9">
+    <row r="134" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="5"/>
-      <c r="B134" s="41"/>
-      <c r="C134" s="42"/>
+      <c r="B134" s="36"/>
+      <c r="C134" s="37"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -3179,10 +2637,10 @@
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
     </row>
-    <row r="135" ht="69.95" customHeight="1" spans="1:9">
+    <row r="135" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="5"/>
-      <c r="B135" s="41"/>
-      <c r="C135" s="42"/>
+      <c r="B135" s="36"/>
+      <c r="C135" s="37"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -3190,10 +2648,10 @@
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
     </row>
-    <row r="136" ht="69.95" customHeight="1" spans="1:9">
+    <row r="136" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="5"/>
-      <c r="B136" s="41"/>
-      <c r="C136" s="42"/>
+      <c r="B136" s="36"/>
+      <c r="C136" s="37"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -3201,10 +2659,10 @@
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
     </row>
-    <row r="137" ht="69.95" customHeight="1" spans="1:9">
+    <row r="137" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="5"/>
-      <c r="B137" s="41"/>
-      <c r="C137" s="42"/>
+      <c r="B137" s="36"/>
+      <c r="C137" s="37"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -3212,10 +2670,10 @@
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
     </row>
-    <row r="138" ht="69.95" customHeight="1" spans="1:9">
+    <row r="138" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="5"/>
-      <c r="B138" s="41"/>
-      <c r="C138" s="42"/>
+      <c r="B138" s="36"/>
+      <c r="C138" s="37"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -3223,10 +2681,10 @@
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
     </row>
-    <row r="139" ht="69.95" customHeight="1" spans="1:9">
+    <row r="139" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="5"/>
-      <c r="B139" s="41"/>
-      <c r="C139" s="42"/>
+      <c r="B139" s="36"/>
+      <c r="C139" s="37"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
@@ -3234,10 +2692,10 @@
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
     </row>
-    <row r="140" ht="69.95" customHeight="1" spans="1:9">
+    <row r="140" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="5"/>
-      <c r="B140" s="41"/>
-      <c r="C140" s="42"/>
+      <c r="B140" s="36"/>
+      <c r="C140" s="37"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -3245,10 +2703,10 @@
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
     </row>
-    <row r="141" ht="69.95" customHeight="1" spans="1:9">
+    <row r="141" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="5"/>
-      <c r="B141" s="41"/>
-      <c r="C141" s="42"/>
+      <c r="B141" s="36"/>
+      <c r="C141" s="37"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -3256,10 +2714,10 @@
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
     </row>
-    <row r="142" ht="69.95" customHeight="1" spans="1:9">
+    <row r="142" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="5"/>
-      <c r="B142" s="41"/>
-      <c r="C142" s="42"/>
+      <c r="B142" s="36"/>
+      <c r="C142" s="37"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -3267,10 +2725,10 @@
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
     </row>
-    <row r="143" ht="69.95" customHeight="1" spans="1:9">
+    <row r="143" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="5"/>
-      <c r="B143" s="41"/>
-      <c r="C143" s="42"/>
+      <c r="B143" s="36"/>
+      <c r="C143" s="37"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -3278,10 +2736,10 @@
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
     </row>
-    <row r="144" ht="69.95" customHeight="1" spans="1:9">
+    <row r="144" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="5"/>
-      <c r="B144" s="41"/>
-      <c r="C144" s="42"/>
+      <c r="B144" s="36"/>
+      <c r="C144" s="37"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -3289,10 +2747,10 @@
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
     </row>
-    <row r="145" ht="69.95" customHeight="1" spans="1:9">
+    <row r="145" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="5"/>
-      <c r="B145" s="41"/>
-      <c r="C145" s="42"/>
+      <c r="B145" s="36"/>
+      <c r="C145" s="37"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -3300,10 +2758,10 @@
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
     </row>
-    <row r="146" ht="69.95" customHeight="1" spans="1:9">
+    <row r="146" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="5"/>
-      <c r="B146" s="41"/>
-      <c r="C146" s="42"/>
+      <c r="B146" s="36"/>
+      <c r="C146" s="37"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -3311,10 +2769,10 @@
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
     </row>
-    <row r="147" ht="69.95" customHeight="1" spans="1:9">
+    <row r="147" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="5"/>
-      <c r="B147" s="41"/>
-      <c r="C147" s="42"/>
+      <c r="B147" s="36"/>
+      <c r="C147" s="37"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -3322,10 +2780,10 @@
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
     </row>
-    <row r="148" ht="69.95" customHeight="1" spans="1:9">
+    <row r="148" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="5"/>
-      <c r="B148" s="41"/>
-      <c r="C148" s="42"/>
+      <c r="B148" s="36"/>
+      <c r="C148" s="37"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -3333,10 +2791,10 @@
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
     </row>
-    <row r="149" ht="69.95" customHeight="1" spans="1:9">
+    <row r="149" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="5"/>
-      <c r="B149" s="41"/>
-      <c r="C149" s="42"/>
+      <c r="B149" s="36"/>
+      <c r="C149" s="37"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -3344,10 +2802,10 @@
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
     </row>
-    <row r="150" ht="69.95" customHeight="1" spans="1:9">
+    <row r="150" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="5"/>
-      <c r="B150" s="41"/>
-      <c r="C150" s="42"/>
+      <c r="B150" s="36"/>
+      <c r="C150" s="37"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -3357,159 +2815,6 @@
     </row>
   </sheetData>
   <mergeCells count="164">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
@@ -3521,9 +2826,163 @@
     <mergeCell ref="H1:I2"/>
     <mergeCell ref="D2:E3"/>
     <mergeCell ref="H3:I4"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:E5"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.590551181102362" right="0.590551181102362" top="1.18110236220472" bottom="0.393700787401575" header="0.984251968503937" footer="0"/>
+  <pageMargins left="0.59055118110236204" right="0.59055118110236204" top="1.1811023622047201" bottom="0.39370078740157499" header="0.98425196850393704" footer="0"/>
   <pageSetup paperSize="9" scale="94" orientation="landscape"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;C                                                                                                                  &amp;"宋体,加粗"   共&amp;N页  第&amp;P页  &amp;"宋体,常规"</oddHeader>
@@ -3534,10 +2993,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="C1:E1"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
@@ -3552,6 +3010,7 @@
     <col min="11" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
@@ -3559,11 +3018,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>

--- a/documents_bin/1818图册目录模板.xlsx
+++ b/documents_bin/1818图册目录模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project\auto-fanban-pre\documents_bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93861D3-CDBD-4E65-A698-2BB6EA098DB5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CE256C-74F3-412E-A0C9-98B3AC18FB55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,17 +20,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -569,7 +564,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -648,8 +643,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -669,71 +724,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1067,21 +1059,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="48"/>
       <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
@@ -1089,58 +1081,58 @@
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="31" t="s">
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="52"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="32" t="s">
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A4" s="13"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="32" t="s">
+      <c r="E4" s="42"/>
+      <c r="F4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="33" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="42"/>
       <c r="F5" s="15"/>
       <c r="G5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="43"/>
+      <c r="H5" s="32"/>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.15">
@@ -1148,58 +1140,58 @@
         <v>11</v>
       </c>
       <c r="B6" s="18"/>
-      <c r="C6" s="40"/>
+      <c r="C6" s="46"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="15"/>
       <c r="G6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="44"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="21"/>
     </row>
     <row r="7" spans="1:28" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="38" t="s">
+      <c r="C7" s="35"/>
+      <c r="D7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="28" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A8" s="39"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
     </row>
     <row r="9" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="37"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
       <c r="D9" s="22"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
@@ -1209,8 +1201,8 @@
     </row>
     <row r="10" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -1220,10 +1212,10 @@
     </row>
     <row r="11" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="22"/>
-      <c r="E11" s="26"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
       <c r="H11" s="24"/>
@@ -1231,1108 +1223,1107 @@
     </row>
     <row r="12" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
       <c r="D12" s="22"/>
-      <c r="E12" s="26"/>
+      <c r="E12" s="23"/>
       <c r="F12" s="24"/>
       <c r="G12" s="24"/>
       <c r="H12" s="24"/>
       <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="26"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="26"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="53"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="53"/>
-      <c r="AB14" s="53"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="25"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="26"/>
     </row>
     <row r="15" spans="1:28" s="5" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="54"/>
-      <c r="U15" s="54"/>
-      <c r="V15" s="54"/>
-      <c r="W15" s="54"/>
-      <c r="X15" s="54"/>
-      <c r="Y15" s="54"/>
-      <c r="Z15" s="54"/>
-      <c r="AA15" s="54"/>
-      <c r="AB15" s="54"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
     </row>
     <row r="16" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="26"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="53"/>
-      <c r="T16" s="53"/>
-      <c r="U16" s="53"/>
-      <c r="V16" s="53"/>
-      <c r="W16" s="53"/>
-      <c r="X16" s="53"/>
-      <c r="Y16" s="53"/>
-      <c r="Z16" s="53"/>
-      <c r="AA16" s="53"/>
-      <c r="AB16" s="53"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="25"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="26"/>
     </row>
     <row r="17" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="26"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="26"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="26"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="26"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="25"/>
     </row>
     <row r="38" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="25"/>
     </row>
     <row r="39" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="25"/>
     </row>
     <row r="40" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="25"/>
     </row>
     <row r="41" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="25"/>
     </row>
     <row r="42" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="25"/>
     </row>
     <row r="43" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="5"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="25"/>
     </row>
     <row r="44" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="25"/>
     </row>
     <row r="45" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="25"/>
     </row>
     <row r="46" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="25"/>
     </row>
     <row r="47" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="5"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="5"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="25"/>
     </row>
     <row r="49" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="5"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="25"/>
     </row>
     <row r="50" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="5"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="25"/>
     </row>
     <row r="51" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="25"/>
     </row>
     <row r="52" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="5"/>
-      <c r="B52" s="36"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="25"/>
     </row>
     <row r="53" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="25"/>
     </row>
     <row r="54" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="5"/>
-      <c r="B54" s="36"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="25"/>
     </row>
     <row r="55" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="5"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="25"/>
     </row>
     <row r="56" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="5"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="25"/>
     </row>
     <row r="57" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="5"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="25"/>
     </row>
     <row r="58" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="5"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="25"/>
     </row>
     <row r="59" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="5"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="25"/>
     </row>
     <row r="60" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="5"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="5"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="5"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="5"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="25"/>
     </row>
     <row r="64" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="5"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="25"/>
     </row>
     <row r="65" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="5"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="25"/>
     </row>
     <row r="66" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="5"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="44"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="23"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="25"/>
     </row>
     <row r="67" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="5"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="44"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="5"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="5"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="44"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="5"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
+      <c r="H70" s="24"/>
+      <c r="I70" s="25"/>
     </row>
     <row r="71" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="5"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="25"/>
     </row>
     <row r="72" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="5"/>
-      <c r="B72" s="36"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
+      <c r="B72" s="43"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="23"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
+      <c r="H72" s="24"/>
+      <c r="I72" s="25"/>
     </row>
     <row r="73" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="5"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="44"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="5"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="44"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="25"/>
     </row>
     <row r="75" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="5"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="44"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="5"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="5"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
+      <c r="B77" s="43"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="5"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-      <c r="I78" s="5"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="44"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="5"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="5"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="44"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
+      <c r="H79" s="24"/>
+      <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="5"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="5"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="25"/>
     </row>
     <row r="81" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="5"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="44"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="24"/>
+      <c r="H81" s="24"/>
+      <c r="I81" s="25"/>
     </row>
     <row r="82" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="5"/>
-      <c r="B82" s="36"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
-      <c r="I82" s="5"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="44"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="24"/>
+      <c r="H82" s="24"/>
+      <c r="I82" s="25"/>
     </row>
     <row r="83" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="5"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="5"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="44"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="24"/>
+      <c r="H83" s="24"/>
+      <c r="I83" s="25"/>
     </row>
     <row r="84" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="5"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="5"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="5"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
+      <c r="H85" s="24"/>
+      <c r="I85" s="25"/>
     </row>
     <row r="86" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="5"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
-      <c r="I86" s="5"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="24"/>
+      <c r="H86" s="24"/>
+      <c r="I86" s="25"/>
     </row>
     <row r="87" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="5"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="44"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="24"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="5"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="5"/>
+      <c r="B88" s="43"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="5"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="5"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="44"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="24"/>
+      <c r="G89" s="24"/>
+      <c r="H89" s="24"/>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="5"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5"/>
+      <c r="B90" s="43"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="24"/>
+      <c r="G90" s="24"/>
+      <c r="H90" s="24"/>
+      <c r="I90" s="25"/>
     </row>
     <row r="91" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="5"/>
-      <c r="B91" s="36"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
-      <c r="I91" s="5"/>
+      <c r="B91" s="43"/>
+      <c r="C91" s="44"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="23"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="24"/>
+      <c r="I91" s="25"/>
     </row>
     <row r="92" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="5"/>
-      <c r="B92" s="36"/>
-      <c r="C92" s="37"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
+      <c r="B92" s="43"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="5"/>
-      <c r="B93" s="36"/>
-      <c r="C93" s="37"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
+      <c r="B93" s="43"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="5"/>
-      <c r="B94" s="36"/>
-      <c r="C94" s="37"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="44"/>
+      <c r="D94" s="22"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="5"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="37"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
+      <c r="B95" s="43"/>
+      <c r="C95" s="44"/>
+      <c r="D95" s="22"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="24"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="25"/>
     </row>
     <row r="96" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="5"/>
-      <c r="B96" s="36"/>
-      <c r="C96" s="37"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
-      <c r="I96" s="5"/>
+      <c r="B96" s="43"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="22"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="5"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
-      <c r="I97" s="5"/>
+      <c r="B97" s="43"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="5"/>
-      <c r="B98" s="36"/>
-      <c r="C98" s="37"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
+      <c r="B98" s="43"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="22"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="5"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="37"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
+      <c r="B99" s="43"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="22"/>
+      <c r="E99" s="23"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="24"/>
+      <c r="H99" s="24"/>
+      <c r="I99" s="25"/>
     </row>
     <row r="100" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="5"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="37"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
+      <c r="B100" s="43"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="22"/>
+      <c r="E100" s="23"/>
+      <c r="F100" s="24"/>
+      <c r="G100" s="24"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="5"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="37"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
+      <c r="B101" s="43"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="22"/>
+      <c r="E101" s="23"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="5"/>
-      <c r="B102" s="36"/>
-      <c r="C102" s="37"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
-      <c r="H102" s="5"/>
-      <c r="I102" s="5"/>
+      <c r="B102" s="43"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="24"/>
+      <c r="I102" s="25"/>
     </row>
     <row r="103" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="5"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="37"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="5"/>
+      <c r="B103" s="43"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="25"/>
     </row>
     <row r="104" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="5"/>
-      <c r="B104" s="36"/>
-      <c r="C104" s="37"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
+      <c r="B104" s="43"/>
+      <c r="C104" s="44"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+      <c r="I104" s="25"/>
     </row>
     <row r="105" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="5"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="37"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="5"/>
+      <c r="B105" s="43"/>
+      <c r="C105" s="44"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="23"/>
+      <c r="F105" s="24"/>
+      <c r="G105" s="24"/>
+      <c r="H105" s="24"/>
+      <c r="I105" s="25"/>
     </row>
     <row r="106" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="5"/>
-      <c r="B106" s="36"/>
-      <c r="C106" s="37"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
+      <c r="B106" s="43"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+      <c r="I106" s="25"/>
     </row>
     <row r="107" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="5"/>
-      <c r="B107" s="36"/>
-      <c r="C107" s="37"/>
+      <c r="B107" s="43"/>
+      <c r="C107" s="44"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
@@ -2342,8 +2333,8 @@
     </row>
     <row r="108" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="5"/>
-      <c r="B108" s="36"/>
-      <c r="C108" s="37"/>
+      <c r="B108" s="43"/>
+      <c r="C108" s="44"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
@@ -2353,8 +2344,8 @@
     </row>
     <row r="109" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="5"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="37"/>
+      <c r="B109" s="43"/>
+      <c r="C109" s="44"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
@@ -2364,8 +2355,8 @@
     </row>
     <row r="110" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="5"/>
-      <c r="B110" s="36"/>
-      <c r="C110" s="37"/>
+      <c r="B110" s="43"/>
+      <c r="C110" s="44"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
@@ -2375,8 +2366,8 @@
     </row>
     <row r="111" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="5"/>
-      <c r="B111" s="36"/>
-      <c r="C111" s="37"/>
+      <c r="B111" s="43"/>
+      <c r="C111" s="44"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
@@ -2386,8 +2377,8 @@
     </row>
     <row r="112" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="5"/>
-      <c r="B112" s="36"/>
-      <c r="C112" s="37"/>
+      <c r="B112" s="43"/>
+      <c r="C112" s="44"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
@@ -2397,8 +2388,8 @@
     </row>
     <row r="113" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="5"/>
-      <c r="B113" s="36"/>
-      <c r="C113" s="37"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="44"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
@@ -2408,8 +2399,8 @@
     </row>
     <row r="114" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="5"/>
-      <c r="B114" s="36"/>
-      <c r="C114" s="37"/>
+      <c r="B114" s="43"/>
+      <c r="C114" s="44"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
@@ -2419,8 +2410,8 @@
     </row>
     <row r="115" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5"/>
-      <c r="B115" s="36"/>
-      <c r="C115" s="37"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="44"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
@@ -2430,8 +2421,8 @@
     </row>
     <row r="116" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5"/>
-      <c r="B116" s="36"/>
-      <c r="C116" s="37"/>
+      <c r="B116" s="43"/>
+      <c r="C116" s="44"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -2441,8 +2432,8 @@
     </row>
     <row r="117" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="5"/>
-      <c r="B117" s="36"/>
-      <c r="C117" s="37"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="44"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -2452,8 +2443,8 @@
     </row>
     <row r="118" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="5"/>
-      <c r="B118" s="36"/>
-      <c r="C118" s="37"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="44"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -2463,8 +2454,8 @@
     </row>
     <row r="119" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="5"/>
-      <c r="B119" s="36"/>
-      <c r="C119" s="37"/>
+      <c r="B119" s="43"/>
+      <c r="C119" s="44"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -2474,8 +2465,8 @@
     </row>
     <row r="120" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="5"/>
-      <c r="B120" s="36"/>
-      <c r="C120" s="37"/>
+      <c r="B120" s="43"/>
+      <c r="C120" s="44"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -2485,8 +2476,8 @@
     </row>
     <row r="121" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="5"/>
-      <c r="B121" s="36"/>
-      <c r="C121" s="37"/>
+      <c r="B121" s="43"/>
+      <c r="C121" s="44"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -2496,8 +2487,8 @@
     </row>
     <row r="122" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="5"/>
-      <c r="B122" s="36"/>
-      <c r="C122" s="37"/>
+      <c r="B122" s="43"/>
+      <c r="C122" s="44"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -2507,8 +2498,8 @@
     </row>
     <row r="123" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="5"/>
-      <c r="B123" s="36"/>
-      <c r="C123" s="37"/>
+      <c r="B123" s="43"/>
+      <c r="C123" s="44"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -2518,8 +2509,8 @@
     </row>
     <row r="124" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5"/>
-      <c r="B124" s="36"/>
-      <c r="C124" s="37"/>
+      <c r="B124" s="43"/>
+      <c r="C124" s="44"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -2529,8 +2520,8 @@
     </row>
     <row r="125" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5"/>
-      <c r="B125" s="36"/>
-      <c r="C125" s="37"/>
+      <c r="B125" s="43"/>
+      <c r="C125" s="44"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -2540,8 +2531,8 @@
     </row>
     <row r="126" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5"/>
-      <c r="B126" s="36"/>
-      <c r="C126" s="37"/>
+      <c r="B126" s="43"/>
+      <c r="C126" s="44"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -2551,8 +2542,8 @@
     </row>
     <row r="127" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5"/>
-      <c r="B127" s="36"/>
-      <c r="C127" s="37"/>
+      <c r="B127" s="43"/>
+      <c r="C127" s="44"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -2562,8 +2553,8 @@
     </row>
     <row r="128" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5"/>
-      <c r="B128" s="36"/>
-      <c r="C128" s="37"/>
+      <c r="B128" s="43"/>
+      <c r="C128" s="44"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -2573,8 +2564,8 @@
     </row>
     <row r="129" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="5"/>
-      <c r="B129" s="36"/>
-      <c r="C129" s="37"/>
+      <c r="B129" s="43"/>
+      <c r="C129" s="44"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -2584,8 +2575,8 @@
     </row>
     <row r="130" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="5"/>
-      <c r="B130" s="36"/>
-      <c r="C130" s="37"/>
+      <c r="B130" s="43"/>
+      <c r="C130" s="44"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -2595,8 +2586,8 @@
     </row>
     <row r="131" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="5"/>
-      <c r="B131" s="36"/>
-      <c r="C131" s="37"/>
+      <c r="B131" s="43"/>
+      <c r="C131" s="44"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -2606,8 +2597,8 @@
     </row>
     <row r="132" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="5"/>
-      <c r="B132" s="36"/>
-      <c r="C132" s="37"/>
+      <c r="B132" s="43"/>
+      <c r="C132" s="44"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -2617,8 +2608,8 @@
     </row>
     <row r="133" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5"/>
-      <c r="B133" s="36"/>
-      <c r="C133" s="37"/>
+      <c r="B133" s="43"/>
+      <c r="C133" s="44"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -2628,8 +2619,8 @@
     </row>
     <row r="134" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="5"/>
-      <c r="B134" s="36"/>
-      <c r="C134" s="37"/>
+      <c r="B134" s="43"/>
+      <c r="C134" s="44"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -2639,8 +2630,8 @@
     </row>
     <row r="135" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="5"/>
-      <c r="B135" s="36"/>
-      <c r="C135" s="37"/>
+      <c r="B135" s="43"/>
+      <c r="C135" s="44"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -2650,8 +2641,8 @@
     </row>
     <row r="136" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="5"/>
-      <c r="B136" s="36"/>
-      <c r="C136" s="37"/>
+      <c r="B136" s="43"/>
+      <c r="C136" s="44"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -2661,8 +2652,8 @@
     </row>
     <row r="137" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="5"/>
-      <c r="B137" s="36"/>
-      <c r="C137" s="37"/>
+      <c r="B137" s="43"/>
+      <c r="C137" s="44"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -2672,8 +2663,8 @@
     </row>
     <row r="138" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="5"/>
-      <c r="B138" s="36"/>
-      <c r="C138" s="37"/>
+      <c r="B138" s="43"/>
+      <c r="C138" s="44"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -2683,8 +2674,8 @@
     </row>
     <row r="139" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="5"/>
-      <c r="B139" s="36"/>
-      <c r="C139" s="37"/>
+      <c r="B139" s="43"/>
+      <c r="C139" s="44"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
@@ -2694,8 +2685,8 @@
     </row>
     <row r="140" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="5"/>
-      <c r="B140" s="36"/>
-      <c r="C140" s="37"/>
+      <c r="B140" s="43"/>
+      <c r="C140" s="44"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -2705,8 +2696,8 @@
     </row>
     <row r="141" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="5"/>
-      <c r="B141" s="36"/>
-      <c r="C141" s="37"/>
+      <c r="B141" s="43"/>
+      <c r="C141" s="44"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -2716,8 +2707,8 @@
     </row>
     <row r="142" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="5"/>
-      <c r="B142" s="36"/>
-      <c r="C142" s="37"/>
+      <c r="B142" s="43"/>
+      <c r="C142" s="44"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -2727,8 +2718,8 @@
     </row>
     <row r="143" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="5"/>
-      <c r="B143" s="36"/>
-      <c r="C143" s="37"/>
+      <c r="B143" s="43"/>
+      <c r="C143" s="44"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -2738,8 +2729,8 @@
     </row>
     <row r="144" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="5"/>
-      <c r="B144" s="36"/>
-      <c r="C144" s="37"/>
+      <c r="B144" s="43"/>
+      <c r="C144" s="44"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -2749,8 +2740,8 @@
     </row>
     <row r="145" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="5"/>
-      <c r="B145" s="36"/>
-      <c r="C145" s="37"/>
+      <c r="B145" s="43"/>
+      <c r="C145" s="44"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -2760,8 +2751,8 @@
     </row>
     <row r="146" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="5"/>
-      <c r="B146" s="36"/>
-      <c r="C146" s="37"/>
+      <c r="B146" s="43"/>
+      <c r="C146" s="44"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -2771,8 +2762,8 @@
     </row>
     <row r="147" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="5"/>
-      <c r="B147" s="36"/>
-      <c r="C147" s="37"/>
+      <c r="B147" s="43"/>
+      <c r="C147" s="44"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -2782,8 +2773,8 @@
     </row>
     <row r="148" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="5"/>
-      <c r="B148" s="36"/>
-      <c r="C148" s="37"/>
+      <c r="B148" s="43"/>
+      <c r="C148" s="44"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -2793,8 +2784,8 @@
     </row>
     <row r="149" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="5"/>
-      <c r="B149" s="36"/>
-      <c r="C149" s="37"/>
+      <c r="B149" s="43"/>
+      <c r="C149" s="44"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -2804,8 +2795,8 @@
     </row>
     <row r="150" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="5"/>
-      <c r="B150" s="36"/>
-      <c r="C150" s="37"/>
+      <c r="B150" s="43"/>
+      <c r="C150" s="44"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -2815,17 +2806,126 @@
     </row>
   </sheetData>
   <mergeCells count="164">
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="H1:I2"/>
-    <mergeCell ref="D2:E3"/>
-    <mergeCell ref="H3:I4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
@@ -2850,126 +2950,17 @@
     <mergeCell ref="B129:C129"/>
     <mergeCell ref="B130:C130"/>
     <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="H1:I2"/>
+    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="H3:I4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -2981,11 +2972,12 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.59055118110236204" right="0.59055118110236204" top="1.1811023622047201" bottom="0.39370078740157499" header="0.98425196850393704" footer="0"/>
-  <pageSetup paperSize="9" scale="94" orientation="landscape"/>
-  <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;C                                                                                                                  &amp;"宋体,加粗"   共&amp;N页  第&amp;P页  &amp;"宋体,常规"</oddHeader>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="1.1811023622047245" bottom="0.39370078740157483" header="0.98425196850393704" footer="0"/>
+  <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R                                                                                                         &amp;"宋体,加粗"共&amp;N页  第&amp;P页
+page &amp;P of &amp;N</oddHeader>
     <firstHeader>&amp;C&amp;"宋体,加粗"
                                                                                                                   共&amp;N页  第&amp;P页</firstHeader>
   </headerFooter>

--- a/documents_bin/1818图册目录模板.xlsx
+++ b/documents_bin/1818图册目录模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project\auto-fanban-pre\documents_bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CE256C-74F3-412E-A0C9-98B3AC18FB55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2293BACE-7409-4F96-A549-BA4194D73BCC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -694,37 +694,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1059,19 +1059,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="44"/>
       <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50" t="s">
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="46"/>
       <c r="H1" s="38"/>
       <c r="I1" s="39"/>
     </row>
@@ -1083,10 +1083,10 @@
       <c r="C2" s="9"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="51"/>
+      <c r="G2" s="47"/>
       <c r="H2" s="40"/>
       <c r="I2" s="41"/>
     </row>
@@ -1096,10 +1096,10 @@
       <c r="C3" s="12"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="52"/>
+      <c r="G3" s="48"/>
       <c r="H3" s="40"/>
       <c r="I3" s="41"/>
     </row>
@@ -1111,19 +1111,19 @@
         <v>6</v>
       </c>
       <c r="E4" s="42"/>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="52"/>
+      <c r="G4" s="48"/>
       <c r="H4" s="40"/>
       <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="42" t="s">
         <v>9</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="18"/>
-      <c r="C6" s="46"/>
+      <c r="C6" s="53"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="15"/>
@@ -1190,8 +1190,8 @@
     </row>
     <row r="9" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="44"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="22"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
@@ -1201,8 +1201,8 @@
     </row>
     <row r="10" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="52"/>
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -1212,8 +1212,8 @@
     </row>
     <row r="11" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="44"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="22"/>
       <c r="E11" s="23"/>
       <c r="F11" s="24"/>
@@ -1223,8 +1223,8 @@
     </row>
     <row r="12" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="52"/>
       <c r="D12" s="22"/>
       <c r="E12" s="23"/>
       <c r="F12" s="24"/>
@@ -1234,8 +1234,8 @@
     </row>
     <row r="13" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="44"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="22"/>
       <c r="E13" s="23"/>
       <c r="F13" s="24"/>
@@ -1245,8 +1245,8 @@
     </row>
     <row r="14" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="22"/>
       <c r="E14" s="23"/>
       <c r="F14" s="24"/>
@@ -1273,8 +1273,8 @@
       <c r="AB14" s="26"/>
     </row>
     <row r="15" spans="1:28" s="5" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="43"/>
-      <c r="C15" s="44"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
       <c r="D15" s="22"/>
       <c r="E15" s="23"/>
       <c r="F15" s="24"/>
@@ -1303,8 +1303,8 @@
     </row>
     <row r="16" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="22"/>
       <c r="E16" s="23"/>
       <c r="F16" s="24"/>
@@ -1332,8 +1332,8 @@
     </row>
     <row r="17" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="44"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="22"/>
       <c r="E17" s="23"/>
       <c r="F17" s="24"/>
@@ -1343,8 +1343,8 @@
     </row>
     <row r="18" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="22"/>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -1354,8 +1354,8 @@
     </row>
     <row r="19" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="22"/>
       <c r="E19" s="23"/>
       <c r="F19" s="24"/>
@@ -1365,8 +1365,8 @@
     </row>
     <row r="20" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="22"/>
       <c r="E20" s="23"/>
       <c r="F20" s="24"/>
@@ -1376,8 +1376,8 @@
     </row>
     <row r="21" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="22"/>
       <c r="E21" s="23"/>
       <c r="F21" s="24"/>
@@ -1387,8 +1387,8 @@
     </row>
     <row r="22" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="22"/>
       <c r="E22" s="23"/>
       <c r="F22" s="24"/>
@@ -1398,8 +1398,8 @@
     </row>
     <row r="23" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="22"/>
       <c r="E23" s="23"/>
       <c r="F23" s="24"/>
@@ -1409,8 +1409,8 @@
     </row>
     <row r="24" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="44"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="22"/>
       <c r="E24" s="23"/>
       <c r="F24" s="24"/>
@@ -1420,8 +1420,8 @@
     </row>
     <row r="25" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="44"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="22"/>
       <c r="E25" s="23"/>
       <c r="F25" s="24"/>
@@ -1431,8 +1431,8 @@
     </row>
     <row r="26" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="44"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="22"/>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -1442,8 +1442,8 @@
     </row>
     <row r="27" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="44"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="22"/>
       <c r="E27" s="23"/>
       <c r="F27" s="24"/>
@@ -1453,8 +1453,8 @@
     </row>
     <row r="28" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="44"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="22"/>
       <c r="E28" s="23"/>
       <c r="F28" s="24"/>
@@ -1464,8 +1464,8 @@
     </row>
     <row r="29" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="44"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="22"/>
       <c r="E29" s="23"/>
       <c r="F29" s="24"/>
@@ -1475,8 +1475,8 @@
     </row>
     <row r="30" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="44"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
       <c r="D30" s="22"/>
       <c r="E30" s="23"/>
       <c r="F30" s="24"/>
@@ -1486,8 +1486,8 @@
     </row>
     <row r="31" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="44"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="52"/>
       <c r="D31" s="22"/>
       <c r="E31" s="23"/>
       <c r="F31" s="24"/>
@@ -1497,8 +1497,8 @@
     </row>
     <row r="32" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="44"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="22"/>
       <c r="E32" s="23"/>
       <c r="F32" s="24"/>
@@ -1508,8 +1508,8 @@
     </row>
     <row r="33" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="44"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="22"/>
       <c r="E33" s="23"/>
       <c r="F33" s="24"/>
@@ -1519,8 +1519,8 @@
     </row>
     <row r="34" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="44"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="22"/>
       <c r="E34" s="23"/>
       <c r="F34" s="24"/>
@@ -1530,8 +1530,8 @@
     </row>
     <row r="35" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="44"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="52"/>
       <c r="D35" s="22"/>
       <c r="E35" s="23"/>
       <c r="F35" s="24"/>
@@ -1541,8 +1541,8 @@
     </row>
     <row r="36" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="44"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="22"/>
       <c r="E36" s="23"/>
       <c r="F36" s="24"/>
@@ -1552,8 +1552,8 @@
     </row>
     <row r="37" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="44"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="22"/>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
@@ -1563,8 +1563,8 @@
     </row>
     <row r="38" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="44"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
       <c r="D38" s="22"/>
       <c r="E38" s="23"/>
       <c r="F38" s="24"/>
@@ -1574,8 +1574,8 @@
     </row>
     <row r="39" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="44"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="52"/>
       <c r="D39" s="22"/>
       <c r="E39" s="23"/>
       <c r="F39" s="24"/>
@@ -1585,8 +1585,8 @@
     </row>
     <row r="40" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="44"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
       <c r="D40" s="22"/>
       <c r="E40" s="23"/>
       <c r="F40" s="24"/>
@@ -1596,8 +1596,8 @@
     </row>
     <row r="41" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="44"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="52"/>
       <c r="D41" s="22"/>
       <c r="E41" s="23"/>
       <c r="F41" s="24"/>
@@ -1607,8 +1607,8 @@
     </row>
     <row r="42" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="44"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
       <c r="D42" s="22"/>
       <c r="E42" s="23"/>
       <c r="F42" s="24"/>
@@ -1618,8 +1618,8 @@
     </row>
     <row r="43" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="5"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="44"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="52"/>
       <c r="D43" s="22"/>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
@@ -1629,8 +1629,8 @@
     </row>
     <row r="44" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="44"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
       <c r="D44" s="22"/>
       <c r="E44" s="23"/>
       <c r="F44" s="24"/>
@@ -1640,8 +1640,8 @@
     </row>
     <row r="45" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="44"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="52"/>
       <c r="D45" s="22"/>
       <c r="E45" s="23"/>
       <c r="F45" s="24"/>
@@ -1651,8 +1651,8 @@
     </row>
     <row r="46" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="44"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
       <c r="D46" s="22"/>
       <c r="E46" s="23"/>
       <c r="F46" s="24"/>
@@ -1662,8 +1662,8 @@
     </row>
     <row r="47" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="5"/>
-      <c r="B47" s="43"/>
-      <c r="C47" s="44"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="22"/>
       <c r="E47" s="23"/>
       <c r="F47" s="24"/>
@@ -1673,8 +1673,8 @@
     </row>
     <row r="48" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="5"/>
-      <c r="B48" s="43"/>
-      <c r="C48" s="44"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="22"/>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
@@ -1684,8 +1684,8 @@
     </row>
     <row r="49" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="5"/>
-      <c r="B49" s="43"/>
-      <c r="C49" s="44"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="22"/>
       <c r="E49" s="23"/>
       <c r="F49" s="24"/>
@@ -1695,8 +1695,8 @@
     </row>
     <row r="50" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="5"/>
-      <c r="B50" s="43"/>
-      <c r="C50" s="44"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="52"/>
       <c r="D50" s="22"/>
       <c r="E50" s="23"/>
       <c r="F50" s="24"/>
@@ -1706,8 +1706,8 @@
     </row>
     <row r="51" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5"/>
-      <c r="B51" s="43"/>
-      <c r="C51" s="44"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="52"/>
       <c r="D51" s="22"/>
       <c r="E51" s="23"/>
       <c r="F51" s="24"/>
@@ -1717,8 +1717,8 @@
     </row>
     <row r="52" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="5"/>
-      <c r="B52" s="43"/>
-      <c r="C52" s="44"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="22"/>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
@@ -1728,8 +1728,8 @@
     </row>
     <row r="53" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
-      <c r="B53" s="43"/>
-      <c r="C53" s="44"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="22"/>
       <c r="E53" s="23"/>
       <c r="F53" s="24"/>
@@ -1739,8 +1739,8 @@
     </row>
     <row r="54" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="5"/>
-      <c r="B54" s="43"/>
-      <c r="C54" s="44"/>
+      <c r="B54" s="51"/>
+      <c r="C54" s="52"/>
       <c r="D54" s="22"/>
       <c r="E54" s="23"/>
       <c r="F54" s="24"/>
@@ -1750,8 +1750,8 @@
     </row>
     <row r="55" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="5"/>
-      <c r="B55" s="43"/>
-      <c r="C55" s="44"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="22"/>
       <c r="E55" s="23"/>
       <c r="F55" s="24"/>
@@ -1761,8 +1761,8 @@
     </row>
     <row r="56" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="5"/>
-      <c r="B56" s="43"/>
-      <c r="C56" s="44"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="22"/>
       <c r="E56" s="23"/>
       <c r="F56" s="24"/>
@@ -1772,8 +1772,8 @@
     </row>
     <row r="57" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="5"/>
-      <c r="B57" s="43"/>
-      <c r="C57" s="44"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="52"/>
       <c r="D57" s="22"/>
       <c r="E57" s="23"/>
       <c r="F57" s="24"/>
@@ -1783,8 +1783,8 @@
     </row>
     <row r="58" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="5"/>
-      <c r="B58" s="43"/>
-      <c r="C58" s="44"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="22"/>
       <c r="E58" s="23"/>
       <c r="F58" s="24"/>
@@ -1794,8 +1794,8 @@
     </row>
     <row r="59" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="5"/>
-      <c r="B59" s="43"/>
-      <c r="C59" s="44"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="52"/>
       <c r="D59" s="22"/>
       <c r="E59" s="23"/>
       <c r="F59" s="24"/>
@@ -1805,8 +1805,8 @@
     </row>
     <row r="60" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="5"/>
-      <c r="B60" s="43"/>
-      <c r="C60" s="44"/>
+      <c r="B60" s="51"/>
+      <c r="C60" s="52"/>
       <c r="D60" s="22"/>
       <c r="E60" s="23"/>
       <c r="F60" s="24"/>
@@ -1816,8 +1816,8 @@
     </row>
     <row r="61" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="5"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="44"/>
+      <c r="B61" s="51"/>
+      <c r="C61" s="52"/>
       <c r="D61" s="22"/>
       <c r="E61" s="23"/>
       <c r="F61" s="24"/>
@@ -1827,8 +1827,8 @@
     </row>
     <row r="62" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="5"/>
-      <c r="B62" s="43"/>
-      <c r="C62" s="44"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="52"/>
       <c r="D62" s="22"/>
       <c r="E62" s="23"/>
       <c r="F62" s="24"/>
@@ -1838,8 +1838,8 @@
     </row>
     <row r="63" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="5"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="44"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="52"/>
       <c r="D63" s="22"/>
       <c r="E63" s="23"/>
       <c r="F63" s="24"/>
@@ -1849,8 +1849,8 @@
     </row>
     <row r="64" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="5"/>
-      <c r="B64" s="43"/>
-      <c r="C64" s="44"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="52"/>
       <c r="D64" s="22"/>
       <c r="E64" s="23"/>
       <c r="F64" s="24"/>
@@ -1860,8 +1860,8 @@
     </row>
     <row r="65" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="5"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="44"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="52"/>
       <c r="D65" s="22"/>
       <c r="E65" s="23"/>
       <c r="F65" s="24"/>
@@ -1871,8 +1871,8 @@
     </row>
     <row r="66" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="5"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="44"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="52"/>
       <c r="D66" s="22"/>
       <c r="E66" s="23"/>
       <c r="F66" s="24"/>
@@ -1882,8 +1882,8 @@
     </row>
     <row r="67" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="5"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="44"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="52"/>
       <c r="D67" s="22"/>
       <c r="E67" s="23"/>
       <c r="F67" s="24"/>
@@ -1893,8 +1893,8 @@
     </row>
     <row r="68" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="5"/>
-      <c r="B68" s="43"/>
-      <c r="C68" s="44"/>
+      <c r="B68" s="51"/>
+      <c r="C68" s="52"/>
       <c r="D68" s="22"/>
       <c r="E68" s="23"/>
       <c r="F68" s="24"/>
@@ -1904,8 +1904,8 @@
     </row>
     <row r="69" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="5"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="44"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="52"/>
       <c r="D69" s="22"/>
       <c r="E69" s="23"/>
       <c r="F69" s="24"/>
@@ -1915,8 +1915,8 @@
     </row>
     <row r="70" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="5"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="44"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="52"/>
       <c r="D70" s="22"/>
       <c r="E70" s="23"/>
       <c r="F70" s="24"/>
@@ -1926,8 +1926,8 @@
     </row>
     <row r="71" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="5"/>
-      <c r="B71" s="43"/>
-      <c r="C71" s="44"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="52"/>
       <c r="D71" s="22"/>
       <c r="E71" s="23"/>
       <c r="F71" s="24"/>
@@ -1937,8 +1937,8 @@
     </row>
     <row r="72" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="5"/>
-      <c r="B72" s="43"/>
-      <c r="C72" s="44"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="52"/>
       <c r="D72" s="22"/>
       <c r="E72" s="23"/>
       <c r="F72" s="24"/>
@@ -1948,8 +1948,8 @@
     </row>
     <row r="73" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="5"/>
-      <c r="B73" s="43"/>
-      <c r="C73" s="44"/>
+      <c r="B73" s="51"/>
+      <c r="C73" s="52"/>
       <c r="D73" s="22"/>
       <c r="E73" s="23"/>
       <c r="F73" s="24"/>
@@ -1959,8 +1959,8 @@
     </row>
     <row r="74" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="5"/>
-      <c r="B74" s="43"/>
-      <c r="C74" s="44"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="52"/>
       <c r="D74" s="22"/>
       <c r="E74" s="23"/>
       <c r="F74" s="24"/>
@@ -1970,8 +1970,8 @@
     </row>
     <row r="75" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="5"/>
-      <c r="B75" s="43"/>
-      <c r="C75" s="44"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="52"/>
       <c r="D75" s="22"/>
       <c r="E75" s="23"/>
       <c r="F75" s="24"/>
@@ -1981,8 +1981,8 @@
     </row>
     <row r="76" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="5"/>
-      <c r="B76" s="43"/>
-      <c r="C76" s="44"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="52"/>
       <c r="D76" s="22"/>
       <c r="E76" s="23"/>
       <c r="F76" s="24"/>
@@ -1992,8 +1992,8 @@
     </row>
     <row r="77" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="5"/>
-      <c r="B77" s="43"/>
-      <c r="C77" s="44"/>
+      <c r="B77" s="51"/>
+      <c r="C77" s="52"/>
       <c r="D77" s="22"/>
       <c r="E77" s="23"/>
       <c r="F77" s="24"/>
@@ -2003,8 +2003,8 @@
     </row>
     <row r="78" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="5"/>
-      <c r="B78" s="43"/>
-      <c r="C78" s="44"/>
+      <c r="B78" s="51"/>
+      <c r="C78" s="52"/>
       <c r="D78" s="22"/>
       <c r="E78" s="23"/>
       <c r="F78" s="24"/>
@@ -2014,8 +2014,8 @@
     </row>
     <row r="79" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="5"/>
-      <c r="B79" s="43"/>
-      <c r="C79" s="44"/>
+      <c r="B79" s="51"/>
+      <c r="C79" s="52"/>
       <c r="D79" s="22"/>
       <c r="E79" s="23"/>
       <c r="F79" s="24"/>
@@ -2025,8 +2025,8 @@
     </row>
     <row r="80" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="5"/>
-      <c r="B80" s="43"/>
-      <c r="C80" s="44"/>
+      <c r="B80" s="51"/>
+      <c r="C80" s="52"/>
       <c r="D80" s="22"/>
       <c r="E80" s="23"/>
       <c r="F80" s="24"/>
@@ -2036,8 +2036,8 @@
     </row>
     <row r="81" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="5"/>
-      <c r="B81" s="43"/>
-      <c r="C81" s="44"/>
+      <c r="B81" s="51"/>
+      <c r="C81" s="52"/>
       <c r="D81" s="22"/>
       <c r="E81" s="23"/>
       <c r="F81" s="24"/>
@@ -2047,8 +2047,8 @@
     </row>
     <row r="82" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="5"/>
-      <c r="B82" s="43"/>
-      <c r="C82" s="44"/>
+      <c r="B82" s="51"/>
+      <c r="C82" s="52"/>
       <c r="D82" s="22"/>
       <c r="E82" s="23"/>
       <c r="F82" s="24"/>
@@ -2058,8 +2058,8 @@
     </row>
     <row r="83" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="5"/>
-      <c r="B83" s="43"/>
-      <c r="C83" s="44"/>
+      <c r="B83" s="51"/>
+      <c r="C83" s="52"/>
       <c r="D83" s="22"/>
       <c r="E83" s="23"/>
       <c r="F83" s="24"/>
@@ -2069,8 +2069,8 @@
     </row>
     <row r="84" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="5"/>
-      <c r="B84" s="43"/>
-      <c r="C84" s="44"/>
+      <c r="B84" s="51"/>
+      <c r="C84" s="52"/>
       <c r="D84" s="22"/>
       <c r="E84" s="23"/>
       <c r="F84" s="24"/>
@@ -2080,8 +2080,8 @@
     </row>
     <row r="85" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="5"/>
-      <c r="B85" s="43"/>
-      <c r="C85" s="44"/>
+      <c r="B85" s="51"/>
+      <c r="C85" s="52"/>
       <c r="D85" s="22"/>
       <c r="E85" s="23"/>
       <c r="F85" s="24"/>
@@ -2091,8 +2091,8 @@
     </row>
     <row r="86" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="5"/>
-      <c r="B86" s="43"/>
-      <c r="C86" s="44"/>
+      <c r="B86" s="51"/>
+      <c r="C86" s="52"/>
       <c r="D86" s="22"/>
       <c r="E86" s="23"/>
       <c r="F86" s="24"/>
@@ -2102,8 +2102,8 @@
     </row>
     <row r="87" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="5"/>
-      <c r="B87" s="43"/>
-      <c r="C87" s="44"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="52"/>
       <c r="D87" s="22"/>
       <c r="E87" s="23"/>
       <c r="F87" s="24"/>
@@ -2113,8 +2113,8 @@
     </row>
     <row r="88" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="5"/>
-      <c r="B88" s="43"/>
-      <c r="C88" s="44"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="52"/>
       <c r="D88" s="22"/>
       <c r="E88" s="23"/>
       <c r="F88" s="24"/>
@@ -2124,8 +2124,8 @@
     </row>
     <row r="89" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="5"/>
-      <c r="B89" s="43"/>
-      <c r="C89" s="44"/>
+      <c r="B89" s="51"/>
+      <c r="C89" s="52"/>
       <c r="D89" s="22"/>
       <c r="E89" s="23"/>
       <c r="F89" s="24"/>
@@ -2135,8 +2135,8 @@
     </row>
     <row r="90" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="5"/>
-      <c r="B90" s="43"/>
-      <c r="C90" s="44"/>
+      <c r="B90" s="51"/>
+      <c r="C90" s="52"/>
       <c r="D90" s="22"/>
       <c r="E90" s="23"/>
       <c r="F90" s="24"/>
@@ -2146,8 +2146,8 @@
     </row>
     <row r="91" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="5"/>
-      <c r="B91" s="43"/>
-      <c r="C91" s="44"/>
+      <c r="B91" s="51"/>
+      <c r="C91" s="52"/>
       <c r="D91" s="22"/>
       <c r="E91" s="23"/>
       <c r="F91" s="24"/>
@@ -2157,8 +2157,8 @@
     </row>
     <row r="92" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="5"/>
-      <c r="B92" s="43"/>
-      <c r="C92" s="44"/>
+      <c r="B92" s="51"/>
+      <c r="C92" s="52"/>
       <c r="D92" s="22"/>
       <c r="E92" s="23"/>
       <c r="F92" s="24"/>
@@ -2168,8 +2168,8 @@
     </row>
     <row r="93" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="5"/>
-      <c r="B93" s="43"/>
-      <c r="C93" s="44"/>
+      <c r="B93" s="51"/>
+      <c r="C93" s="52"/>
       <c r="D93" s="22"/>
       <c r="E93" s="23"/>
       <c r="F93" s="24"/>
@@ -2179,8 +2179,8 @@
     </row>
     <row r="94" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="5"/>
-      <c r="B94" s="43"/>
-      <c r="C94" s="44"/>
+      <c r="B94" s="51"/>
+      <c r="C94" s="52"/>
       <c r="D94" s="22"/>
       <c r="E94" s="23"/>
       <c r="F94" s="24"/>
@@ -2190,8 +2190,8 @@
     </row>
     <row r="95" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="5"/>
-      <c r="B95" s="43"/>
-      <c r="C95" s="44"/>
+      <c r="B95" s="51"/>
+      <c r="C95" s="52"/>
       <c r="D95" s="22"/>
       <c r="E95" s="23"/>
       <c r="F95" s="24"/>
@@ -2201,8 +2201,8 @@
     </row>
     <row r="96" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="5"/>
-      <c r="B96" s="43"/>
-      <c r="C96" s="44"/>
+      <c r="B96" s="51"/>
+      <c r="C96" s="52"/>
       <c r="D96" s="22"/>
       <c r="E96" s="23"/>
       <c r="F96" s="24"/>
@@ -2212,8 +2212,8 @@
     </row>
     <row r="97" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="5"/>
-      <c r="B97" s="43"/>
-      <c r="C97" s="44"/>
+      <c r="B97" s="51"/>
+      <c r="C97" s="52"/>
       <c r="D97" s="22"/>
       <c r="E97" s="23"/>
       <c r="F97" s="24"/>
@@ -2223,8 +2223,8 @@
     </row>
     <row r="98" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="5"/>
-      <c r="B98" s="43"/>
-      <c r="C98" s="44"/>
+      <c r="B98" s="51"/>
+      <c r="C98" s="52"/>
       <c r="D98" s="22"/>
       <c r="E98" s="23"/>
       <c r="F98" s="24"/>
@@ -2234,8 +2234,8 @@
     </row>
     <row r="99" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="5"/>
-      <c r="B99" s="43"/>
-      <c r="C99" s="44"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="52"/>
       <c r="D99" s="22"/>
       <c r="E99" s="23"/>
       <c r="F99" s="24"/>
@@ -2245,8 +2245,8 @@
     </row>
     <row r="100" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="5"/>
-      <c r="B100" s="43"/>
-      <c r="C100" s="44"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="52"/>
       <c r="D100" s="22"/>
       <c r="E100" s="23"/>
       <c r="F100" s="24"/>
@@ -2256,8 +2256,8 @@
     </row>
     <row r="101" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="5"/>
-      <c r="B101" s="43"/>
-      <c r="C101" s="44"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="52"/>
       <c r="D101" s="22"/>
       <c r="E101" s="23"/>
       <c r="F101" s="24"/>
@@ -2267,8 +2267,8 @@
     </row>
     <row r="102" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="5"/>
-      <c r="B102" s="43"/>
-      <c r="C102" s="44"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="52"/>
       <c r="D102" s="22"/>
       <c r="E102" s="23"/>
       <c r="F102" s="24"/>
@@ -2278,8 +2278,8 @@
     </row>
     <row r="103" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="5"/>
-      <c r="B103" s="43"/>
-      <c r="C103" s="44"/>
+      <c r="B103" s="51"/>
+      <c r="C103" s="52"/>
       <c r="D103" s="22"/>
       <c r="E103" s="23"/>
       <c r="F103" s="24"/>
@@ -2289,8 +2289,8 @@
     </row>
     <row r="104" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="5"/>
-      <c r="B104" s="43"/>
-      <c r="C104" s="44"/>
+      <c r="B104" s="51"/>
+      <c r="C104" s="52"/>
       <c r="D104" s="22"/>
       <c r="E104" s="23"/>
       <c r="F104" s="24"/>
@@ -2300,8 +2300,8 @@
     </row>
     <row r="105" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="5"/>
-      <c r="B105" s="43"/>
-      <c r="C105" s="44"/>
+      <c r="B105" s="51"/>
+      <c r="C105" s="52"/>
       <c r="D105" s="22"/>
       <c r="E105" s="23"/>
       <c r="F105" s="24"/>
@@ -2311,8 +2311,8 @@
     </row>
     <row r="106" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="5"/>
-      <c r="B106" s="43"/>
-      <c r="C106" s="44"/>
+      <c r="B106" s="51"/>
+      <c r="C106" s="52"/>
       <c r="D106" s="22"/>
       <c r="E106" s="23"/>
       <c r="F106" s="24"/>
@@ -2322,8 +2322,8 @@
     </row>
     <row r="107" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="5"/>
-      <c r="B107" s="43"/>
-      <c r="C107" s="44"/>
+      <c r="B107" s="51"/>
+      <c r="C107" s="52"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
@@ -2333,8 +2333,8 @@
     </row>
     <row r="108" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="5"/>
-      <c r="B108" s="43"/>
-      <c r="C108" s="44"/>
+      <c r="B108" s="51"/>
+      <c r="C108" s="52"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
@@ -2344,8 +2344,8 @@
     </row>
     <row r="109" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="5"/>
-      <c r="B109" s="43"/>
-      <c r="C109" s="44"/>
+      <c r="B109" s="51"/>
+      <c r="C109" s="52"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
@@ -2355,8 +2355,8 @@
     </row>
     <row r="110" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="5"/>
-      <c r="B110" s="43"/>
-      <c r="C110" s="44"/>
+      <c r="B110" s="51"/>
+      <c r="C110" s="52"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
@@ -2366,8 +2366,8 @@
     </row>
     <row r="111" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="5"/>
-      <c r="B111" s="43"/>
-      <c r="C111" s="44"/>
+      <c r="B111" s="51"/>
+      <c r="C111" s="52"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
@@ -2377,8 +2377,8 @@
     </row>
     <row r="112" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="5"/>
-      <c r="B112" s="43"/>
-      <c r="C112" s="44"/>
+      <c r="B112" s="51"/>
+      <c r="C112" s="52"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
@@ -2388,8 +2388,8 @@
     </row>
     <row r="113" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="5"/>
-      <c r="B113" s="43"/>
-      <c r="C113" s="44"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="52"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
@@ -2399,8 +2399,8 @@
     </row>
     <row r="114" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="5"/>
-      <c r="B114" s="43"/>
-      <c r="C114" s="44"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="52"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
@@ -2410,8 +2410,8 @@
     </row>
     <row r="115" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5"/>
-      <c r="B115" s="43"/>
-      <c r="C115" s="44"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="52"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
@@ -2421,8 +2421,8 @@
     </row>
     <row r="116" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5"/>
-      <c r="B116" s="43"/>
-      <c r="C116" s="44"/>
+      <c r="B116" s="51"/>
+      <c r="C116" s="52"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -2432,8 +2432,8 @@
     </row>
     <row r="117" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="5"/>
-      <c r="B117" s="43"/>
-      <c r="C117" s="44"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="52"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -2443,8 +2443,8 @@
     </row>
     <row r="118" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="5"/>
-      <c r="B118" s="43"/>
-      <c r="C118" s="44"/>
+      <c r="B118" s="51"/>
+      <c r="C118" s="52"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -2454,8 +2454,8 @@
     </row>
     <row r="119" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="5"/>
-      <c r="B119" s="43"/>
-      <c r="C119" s="44"/>
+      <c r="B119" s="51"/>
+      <c r="C119" s="52"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -2465,8 +2465,8 @@
     </row>
     <row r="120" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="5"/>
-      <c r="B120" s="43"/>
-      <c r="C120" s="44"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="52"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -2476,8 +2476,8 @@
     </row>
     <row r="121" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="5"/>
-      <c r="B121" s="43"/>
-      <c r="C121" s="44"/>
+      <c r="B121" s="51"/>
+      <c r="C121" s="52"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -2487,8 +2487,8 @@
     </row>
     <row r="122" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="5"/>
-      <c r="B122" s="43"/>
-      <c r="C122" s="44"/>
+      <c r="B122" s="51"/>
+      <c r="C122" s="52"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -2498,8 +2498,8 @@
     </row>
     <row r="123" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="5"/>
-      <c r="B123" s="43"/>
-      <c r="C123" s="44"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="52"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -2509,8 +2509,8 @@
     </row>
     <row r="124" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5"/>
-      <c r="B124" s="43"/>
-      <c r="C124" s="44"/>
+      <c r="B124" s="51"/>
+      <c r="C124" s="52"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -2520,8 +2520,8 @@
     </row>
     <row r="125" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5"/>
-      <c r="B125" s="43"/>
-      <c r="C125" s="44"/>
+      <c r="B125" s="51"/>
+      <c r="C125" s="52"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -2531,8 +2531,8 @@
     </row>
     <row r="126" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5"/>
-      <c r="B126" s="43"/>
-      <c r="C126" s="44"/>
+      <c r="B126" s="51"/>
+      <c r="C126" s="52"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -2542,8 +2542,8 @@
     </row>
     <row r="127" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5"/>
-      <c r="B127" s="43"/>
-      <c r="C127" s="44"/>
+      <c r="B127" s="51"/>
+      <c r="C127" s="52"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -2553,8 +2553,8 @@
     </row>
     <row r="128" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5"/>
-      <c r="B128" s="43"/>
-      <c r="C128" s="44"/>
+      <c r="B128" s="51"/>
+      <c r="C128" s="52"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -2564,8 +2564,8 @@
     </row>
     <row r="129" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="5"/>
-      <c r="B129" s="43"/>
-      <c r="C129" s="44"/>
+      <c r="B129" s="51"/>
+      <c r="C129" s="52"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -2575,8 +2575,8 @@
     </row>
     <row r="130" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="5"/>
-      <c r="B130" s="43"/>
-      <c r="C130" s="44"/>
+      <c r="B130" s="51"/>
+      <c r="C130" s="52"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -2586,8 +2586,8 @@
     </row>
     <row r="131" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="5"/>
-      <c r="B131" s="43"/>
-      <c r="C131" s="44"/>
+      <c r="B131" s="51"/>
+      <c r="C131" s="52"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -2597,8 +2597,8 @@
     </row>
     <row r="132" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="5"/>
-      <c r="B132" s="43"/>
-      <c r="C132" s="44"/>
+      <c r="B132" s="51"/>
+      <c r="C132" s="52"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -2608,8 +2608,8 @@
     </row>
     <row r="133" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5"/>
-      <c r="B133" s="43"/>
-      <c r="C133" s="44"/>
+      <c r="B133" s="51"/>
+      <c r="C133" s="52"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -2619,8 +2619,8 @@
     </row>
     <row r="134" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="5"/>
-      <c r="B134" s="43"/>
-      <c r="C134" s="44"/>
+      <c r="B134" s="51"/>
+      <c r="C134" s="52"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -2630,8 +2630,8 @@
     </row>
     <row r="135" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="5"/>
-      <c r="B135" s="43"/>
-      <c r="C135" s="44"/>
+      <c r="B135" s="51"/>
+      <c r="C135" s="52"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -2641,8 +2641,8 @@
     </row>
     <row r="136" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="5"/>
-      <c r="B136" s="43"/>
-      <c r="C136" s="44"/>
+      <c r="B136" s="51"/>
+      <c r="C136" s="52"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -2652,8 +2652,8 @@
     </row>
     <row r="137" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="5"/>
-      <c r="B137" s="43"/>
-      <c r="C137" s="44"/>
+      <c r="B137" s="51"/>
+      <c r="C137" s="52"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -2663,8 +2663,8 @@
     </row>
     <row r="138" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="5"/>
-      <c r="B138" s="43"/>
-      <c r="C138" s="44"/>
+      <c r="B138" s="51"/>
+      <c r="C138" s="52"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -2674,8 +2674,8 @@
     </row>
     <row r="139" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="5"/>
-      <c r="B139" s="43"/>
-      <c r="C139" s="44"/>
+      <c r="B139" s="51"/>
+      <c r="C139" s="52"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
@@ -2685,8 +2685,8 @@
     </row>
     <row r="140" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="5"/>
-      <c r="B140" s="43"/>
-      <c r="C140" s="44"/>
+      <c r="B140" s="51"/>
+      <c r="C140" s="52"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -2696,8 +2696,8 @@
     </row>
     <row r="141" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="5"/>
-      <c r="B141" s="43"/>
-      <c r="C141" s="44"/>
+      <c r="B141" s="51"/>
+      <c r="C141" s="52"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -2707,8 +2707,8 @@
     </row>
     <row r="142" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="5"/>
-      <c r="B142" s="43"/>
-      <c r="C142" s="44"/>
+      <c r="B142" s="51"/>
+      <c r="C142" s="52"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -2718,8 +2718,8 @@
     </row>
     <row r="143" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="5"/>
-      <c r="B143" s="43"/>
-      <c r="C143" s="44"/>
+      <c r="B143" s="51"/>
+      <c r="C143" s="52"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -2729,8 +2729,8 @@
     </row>
     <row r="144" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="5"/>
-      <c r="B144" s="43"/>
-      <c r="C144" s="44"/>
+      <c r="B144" s="51"/>
+      <c r="C144" s="52"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -2740,8 +2740,8 @@
     </row>
     <row r="145" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="5"/>
-      <c r="B145" s="43"/>
-      <c r="C145" s="44"/>
+      <c r="B145" s="51"/>
+      <c r="C145" s="52"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -2751,8 +2751,8 @@
     </row>
     <row r="146" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="5"/>
-      <c r="B146" s="43"/>
-      <c r="C146" s="44"/>
+      <c r="B146" s="51"/>
+      <c r="C146" s="52"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -2762,8 +2762,8 @@
     </row>
     <row r="147" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="5"/>
-      <c r="B147" s="43"/>
-      <c r="C147" s="44"/>
+      <c r="B147" s="51"/>
+      <c r="C147" s="52"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -2773,8 +2773,8 @@
     </row>
     <row r="148" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="5"/>
-      <c r="B148" s="43"/>
-      <c r="C148" s="44"/>
+      <c r="B148" s="51"/>
+      <c r="C148" s="52"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -2784,8 +2784,8 @@
     </row>
     <row r="149" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="5"/>
-      <c r="B149" s="43"/>
-      <c r="C149" s="44"/>
+      <c r="B149" s="51"/>
+      <c r="C149" s="52"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -2795,8 +2795,8 @@
     </row>
     <row r="150" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="5"/>
-      <c r="B150" s="43"/>
-      <c r="C150" s="44"/>
+      <c r="B150" s="51"/>
+      <c r="C150" s="52"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -2972,11 +2972,12 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="1.1811023622047245" bottom="0.39370078740157483" header="0.98425196850393704" footer="0"/>
   <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;R                                                                                                         &amp;"宋体,加粗"共&amp;N页  第&amp;P页
+  <headerFooter alignWithMargins="0">
+    <oddHeader>&amp;R                                                                                                         
+&amp;"宋体,加粗"共&amp;N页  第&amp;P页
 page &amp;P of &amp;N</oddHeader>
     <firstHeader>&amp;C&amp;"宋体,加粗"
                                                                                                                   共&amp;N页  第&amp;P页</firstHeader>

--- a/documents_bin/1818图册目录模板.xlsx
+++ b/documents_bin/1818图册目录模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project\auto-fanban-pre\documents_bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2293BACE-7409-4F96-A549-BA4194D73BCC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956CAF17-E768-4729-B251-1927D0BD0432}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,18 +649,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -713,18 +725,6 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1059,21 +1059,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
+      <c r="B1" s="48"/>
       <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="39"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
@@ -1081,58 +1081,58 @@
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="47" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="48" t="s">
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="41"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="45"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A4" s="13"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="48" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="41"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="42" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="42"/>
+      <c r="E5" s="46"/>
       <c r="F5" s="15"/>
       <c r="G5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="32"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.15">
@@ -1140,49 +1140,49 @@
         <v>11</v>
       </c>
       <c r="B6" s="18"/>
-      <c r="C6" s="53"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="15"/>
       <c r="G6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="33"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="21"/>
     </row>
     <row r="7" spans="1:28" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="28" t="s">
+      <c r="C7" s="39"/>
+      <c r="D7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="30" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A8" s="31"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="30"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="H8" s="31"/>
@@ -1190,8 +1190,8 @@
     </row>
     <row r="9" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="22"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
@@ -1201,8 +1201,8 @@
     </row>
     <row r="10" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="52"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -1212,8 +1212,8 @@
     </row>
     <row r="11" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="52"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="22"/>
       <c r="E11" s="23"/>
       <c r="F11" s="24"/>
@@ -1223,8 +1223,8 @@
     </row>
     <row r="12" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="22"/>
       <c r="E12" s="23"/>
       <c r="F12" s="24"/>
@@ -1234,8 +1234,8 @@
     </row>
     <row r="13" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="22"/>
       <c r="E13" s="23"/>
       <c r="F13" s="24"/>
@@ -1245,8 +1245,8 @@
     </row>
     <row r="14" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="52"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
       <c r="D14" s="22"/>
       <c r="E14" s="23"/>
       <c r="F14" s="24"/>
@@ -1273,8 +1273,8 @@
       <c r="AB14" s="26"/>
     </row>
     <row r="15" spans="1:28" s="5" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="22"/>
       <c r="E15" s="23"/>
       <c r="F15" s="24"/>
@@ -1303,8 +1303,8 @@
     </row>
     <row r="16" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="22"/>
       <c r="E16" s="23"/>
       <c r="F16" s="24"/>
@@ -1332,8 +1332,8 @@
     </row>
     <row r="17" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="22"/>
       <c r="E17" s="23"/>
       <c r="F17" s="24"/>
@@ -1343,8 +1343,8 @@
     </row>
     <row r="18" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="22"/>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -1354,8 +1354,8 @@
     </row>
     <row r="19" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="22"/>
       <c r="E19" s="23"/>
       <c r="F19" s="24"/>
@@ -1365,8 +1365,8 @@
     </row>
     <row r="20" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="22"/>
       <c r="E20" s="23"/>
       <c r="F20" s="24"/>
@@ -1376,8 +1376,8 @@
     </row>
     <row r="21" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="22"/>
       <c r="E21" s="23"/>
       <c r="F21" s="24"/>
@@ -1387,8 +1387,8 @@
     </row>
     <row r="22" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="52"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
       <c r="D22" s="22"/>
       <c r="E22" s="23"/>
       <c r="F22" s="24"/>
@@ -1398,8 +1398,8 @@
     </row>
     <row r="23" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
       <c r="D23" s="22"/>
       <c r="E23" s="23"/>
       <c r="F23" s="24"/>
@@ -1409,8 +1409,8 @@
     </row>
     <row r="24" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="52"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
       <c r="D24" s="22"/>
       <c r="E24" s="23"/>
       <c r="F24" s="24"/>
@@ -1420,8 +1420,8 @@
     </row>
     <row r="25" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
       <c r="D25" s="22"/>
       <c r="E25" s="23"/>
       <c r="F25" s="24"/>
@@ -1431,8 +1431,8 @@
     </row>
     <row r="26" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="52"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="22"/>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -1442,8 +1442,8 @@
     </row>
     <row r="27" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="52"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
       <c r="D27" s="22"/>
       <c r="E27" s="23"/>
       <c r="F27" s="24"/>
@@ -1453,8 +1453,8 @@
     </row>
     <row r="28" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="52"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
       <c r="D28" s="22"/>
       <c r="E28" s="23"/>
       <c r="F28" s="24"/>
@@ -1464,8 +1464,8 @@
     </row>
     <row r="29" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
       <c r="D29" s="22"/>
       <c r="E29" s="23"/>
       <c r="F29" s="24"/>
@@ -1475,8 +1475,8 @@
     </row>
     <row r="30" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
       <c r="D30" s="22"/>
       <c r="E30" s="23"/>
       <c r="F30" s="24"/>
@@ -1486,8 +1486,8 @@
     </row>
     <row r="31" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="52"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
       <c r="D31" s="22"/>
       <c r="E31" s="23"/>
       <c r="F31" s="24"/>
@@ -1497,8 +1497,8 @@
     </row>
     <row r="32" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
       <c r="D32" s="22"/>
       <c r="E32" s="23"/>
       <c r="F32" s="24"/>
@@ -1508,8 +1508,8 @@
     </row>
     <row r="33" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="52"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="29"/>
       <c r="D33" s="22"/>
       <c r="E33" s="23"/>
       <c r="F33" s="24"/>
@@ -1519,8 +1519,8 @@
     </row>
     <row r="34" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="29"/>
       <c r="D34" s="22"/>
       <c r="E34" s="23"/>
       <c r="F34" s="24"/>
@@ -1530,8 +1530,8 @@
     </row>
     <row r="35" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="52"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="22"/>
       <c r="E35" s="23"/>
       <c r="F35" s="24"/>
@@ -1541,8 +1541,8 @@
     </row>
     <row r="36" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="52"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="29"/>
       <c r="D36" s="22"/>
       <c r="E36" s="23"/>
       <c r="F36" s="24"/>
@@ -1552,8 +1552,8 @@
     </row>
     <row r="37" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="29"/>
       <c r="D37" s="22"/>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
@@ -1563,8 +1563,8 @@
     </row>
     <row r="38" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="29"/>
       <c r="D38" s="22"/>
       <c r="E38" s="23"/>
       <c r="F38" s="24"/>
@@ -1574,8 +1574,8 @@
     </row>
     <row r="39" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="52"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="29"/>
       <c r="D39" s="22"/>
       <c r="E39" s="23"/>
       <c r="F39" s="24"/>
@@ -1585,8 +1585,8 @@
     </row>
     <row r="40" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="29"/>
       <c r="D40" s="22"/>
       <c r="E40" s="23"/>
       <c r="F40" s="24"/>
@@ -1596,8 +1596,8 @@
     </row>
     <row r="41" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="52"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
       <c r="D41" s="22"/>
       <c r="E41" s="23"/>
       <c r="F41" s="24"/>
@@ -1607,8 +1607,8 @@
     </row>
     <row r="42" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="29"/>
       <c r="D42" s="22"/>
       <c r="E42" s="23"/>
       <c r="F42" s="24"/>
@@ -1618,8 +1618,8 @@
     </row>
     <row r="43" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="5"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="52"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
       <c r="D43" s="22"/>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
@@ -1629,8 +1629,8 @@
     </row>
     <row r="44" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="22"/>
       <c r="E44" s="23"/>
       <c r="F44" s="24"/>
@@ -1640,8 +1640,8 @@
     </row>
     <row r="45" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="52"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="29"/>
       <c r="D45" s="22"/>
       <c r="E45" s="23"/>
       <c r="F45" s="24"/>
@@ -1651,8 +1651,8 @@
     </row>
     <row r="46" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="29"/>
       <c r="D46" s="22"/>
       <c r="E46" s="23"/>
       <c r="F46" s="24"/>
@@ -1662,8 +1662,8 @@
     </row>
     <row r="47" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="5"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="52"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="29"/>
       <c r="D47" s="22"/>
       <c r="E47" s="23"/>
       <c r="F47" s="24"/>
@@ -1673,8 +1673,8 @@
     </row>
     <row r="48" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="5"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="52"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="29"/>
       <c r="D48" s="22"/>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
@@ -1684,8 +1684,8 @@
     </row>
     <row r="49" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="5"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="52"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="29"/>
       <c r="D49" s="22"/>
       <c r="E49" s="23"/>
       <c r="F49" s="24"/>
@@ -1695,8 +1695,8 @@
     </row>
     <row r="50" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="5"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="52"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="29"/>
       <c r="D50" s="22"/>
       <c r="E50" s="23"/>
       <c r="F50" s="24"/>
@@ -1706,8 +1706,8 @@
     </row>
     <row r="51" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="52"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="22"/>
       <c r="E51" s="23"/>
       <c r="F51" s="24"/>
@@ -1717,8 +1717,8 @@
     </row>
     <row r="52" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="5"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="52"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="29"/>
       <c r="D52" s="22"/>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
@@ -1728,8 +1728,8 @@
     </row>
     <row r="53" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="52"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="29"/>
       <c r="D53" s="22"/>
       <c r="E53" s="23"/>
       <c r="F53" s="24"/>
@@ -1739,8 +1739,8 @@
     </row>
     <row r="54" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="5"/>
-      <c r="B54" s="51"/>
-      <c r="C54" s="52"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="29"/>
       <c r="D54" s="22"/>
       <c r="E54" s="23"/>
       <c r="F54" s="24"/>
@@ -1750,8 +1750,8 @@
     </row>
     <row r="55" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="5"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="52"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="22"/>
       <c r="E55" s="23"/>
       <c r="F55" s="24"/>
@@ -1761,8 +1761,8 @@
     </row>
     <row r="56" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="5"/>
-      <c r="B56" s="51"/>
-      <c r="C56" s="52"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="22"/>
       <c r="E56" s="23"/>
       <c r="F56" s="24"/>
@@ -1772,8 +1772,8 @@
     </row>
     <row r="57" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="5"/>
-      <c r="B57" s="51"/>
-      <c r="C57" s="52"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="22"/>
       <c r="E57" s="23"/>
       <c r="F57" s="24"/>
@@ -1783,8 +1783,8 @@
     </row>
     <row r="58" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="5"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="52"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="29"/>
       <c r="D58" s="22"/>
       <c r="E58" s="23"/>
       <c r="F58" s="24"/>
@@ -1794,8 +1794,8 @@
     </row>
     <row r="59" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="5"/>
-      <c r="B59" s="51"/>
-      <c r="C59" s="52"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="22"/>
       <c r="E59" s="23"/>
       <c r="F59" s="24"/>
@@ -1805,8 +1805,8 @@
     </row>
     <row r="60" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="5"/>
-      <c r="B60" s="51"/>
-      <c r="C60" s="52"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="22"/>
       <c r="E60" s="23"/>
       <c r="F60" s="24"/>
@@ -1816,8 +1816,8 @@
     </row>
     <row r="61" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="5"/>
-      <c r="B61" s="51"/>
-      <c r="C61" s="52"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="22"/>
       <c r="E61" s="23"/>
       <c r="F61" s="24"/>
@@ -1827,8 +1827,8 @@
     </row>
     <row r="62" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="5"/>
-      <c r="B62" s="51"/>
-      <c r="C62" s="52"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="29"/>
       <c r="D62" s="22"/>
       <c r="E62" s="23"/>
       <c r="F62" s="24"/>
@@ -1838,8 +1838,8 @@
     </row>
     <row r="63" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="5"/>
-      <c r="B63" s="51"/>
-      <c r="C63" s="52"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="22"/>
       <c r="E63" s="23"/>
       <c r="F63" s="24"/>
@@ -1849,8 +1849,8 @@
     </row>
     <row r="64" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="5"/>
-      <c r="B64" s="51"/>
-      <c r="C64" s="52"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="22"/>
       <c r="E64" s="23"/>
       <c r="F64" s="24"/>
@@ -1860,8 +1860,8 @@
     </row>
     <row r="65" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="5"/>
-      <c r="B65" s="51"/>
-      <c r="C65" s="52"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="22"/>
       <c r="E65" s="23"/>
       <c r="F65" s="24"/>
@@ -1871,8 +1871,8 @@
     </row>
     <row r="66" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="5"/>
-      <c r="B66" s="51"/>
-      <c r="C66" s="52"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="29"/>
       <c r="D66" s="22"/>
       <c r="E66" s="23"/>
       <c r="F66" s="24"/>
@@ -1882,8 +1882,8 @@
     </row>
     <row r="67" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="5"/>
-      <c r="B67" s="51"/>
-      <c r="C67" s="52"/>
+      <c r="B67" s="28"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="22"/>
       <c r="E67" s="23"/>
       <c r="F67" s="24"/>
@@ -1893,8 +1893,8 @@
     </row>
     <row r="68" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="5"/>
-      <c r="B68" s="51"/>
-      <c r="C68" s="52"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="29"/>
       <c r="D68" s="22"/>
       <c r="E68" s="23"/>
       <c r="F68" s="24"/>
@@ -1904,8 +1904,8 @@
     </row>
     <row r="69" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="5"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="52"/>
+      <c r="B69" s="28"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="22"/>
       <c r="E69" s="23"/>
       <c r="F69" s="24"/>
@@ -1915,8 +1915,8 @@
     </row>
     <row r="70" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="5"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="52"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="29"/>
       <c r="D70" s="22"/>
       <c r="E70" s="23"/>
       <c r="F70" s="24"/>
@@ -1926,8 +1926,8 @@
     </row>
     <row r="71" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="5"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="52"/>
+      <c r="B71" s="28"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="22"/>
       <c r="E71" s="23"/>
       <c r="F71" s="24"/>
@@ -1937,8 +1937,8 @@
     </row>
     <row r="72" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="5"/>
-      <c r="B72" s="51"/>
-      <c r="C72" s="52"/>
+      <c r="B72" s="28"/>
+      <c r="C72" s="29"/>
       <c r="D72" s="22"/>
       <c r="E72" s="23"/>
       <c r="F72" s="24"/>
@@ -1948,8 +1948,8 @@
     </row>
     <row r="73" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="5"/>
-      <c r="B73" s="51"/>
-      <c r="C73" s="52"/>
+      <c r="B73" s="28"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="22"/>
       <c r="E73" s="23"/>
       <c r="F73" s="24"/>
@@ -1959,8 +1959,8 @@
     </row>
     <row r="74" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="5"/>
-      <c r="B74" s="51"/>
-      <c r="C74" s="52"/>
+      <c r="B74" s="28"/>
+      <c r="C74" s="29"/>
       <c r="D74" s="22"/>
       <c r="E74" s="23"/>
       <c r="F74" s="24"/>
@@ -1970,8 +1970,8 @@
     </row>
     <row r="75" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="5"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="52"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="22"/>
       <c r="E75" s="23"/>
       <c r="F75" s="24"/>
@@ -1981,8 +1981,8 @@
     </row>
     <row r="76" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="5"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="52"/>
+      <c r="B76" s="28"/>
+      <c r="C76" s="29"/>
       <c r="D76" s="22"/>
       <c r="E76" s="23"/>
       <c r="F76" s="24"/>
@@ -1992,8 +1992,8 @@
     </row>
     <row r="77" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="5"/>
-      <c r="B77" s="51"/>
-      <c r="C77" s="52"/>
+      <c r="B77" s="28"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="22"/>
       <c r="E77" s="23"/>
       <c r="F77" s="24"/>
@@ -2003,8 +2003,8 @@
     </row>
     <row r="78" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="5"/>
-      <c r="B78" s="51"/>
-      <c r="C78" s="52"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="22"/>
       <c r="E78" s="23"/>
       <c r="F78" s="24"/>
@@ -2014,8 +2014,8 @@
     </row>
     <row r="79" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="5"/>
-      <c r="B79" s="51"/>
-      <c r="C79" s="52"/>
+      <c r="B79" s="28"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="22"/>
       <c r="E79" s="23"/>
       <c r="F79" s="24"/>
@@ -2025,8 +2025,8 @@
     </row>
     <row r="80" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="5"/>
-      <c r="B80" s="51"/>
-      <c r="C80" s="52"/>
+      <c r="B80" s="28"/>
+      <c r="C80" s="29"/>
       <c r="D80" s="22"/>
       <c r="E80" s="23"/>
       <c r="F80" s="24"/>
@@ -2036,8 +2036,8 @@
     </row>
     <row r="81" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="5"/>
-      <c r="B81" s="51"/>
-      <c r="C81" s="52"/>
+      <c r="B81" s="28"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="22"/>
       <c r="E81" s="23"/>
       <c r="F81" s="24"/>
@@ -2047,8 +2047,8 @@
     </row>
     <row r="82" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="5"/>
-      <c r="B82" s="51"/>
-      <c r="C82" s="52"/>
+      <c r="B82" s="28"/>
+      <c r="C82" s="29"/>
       <c r="D82" s="22"/>
       <c r="E82" s="23"/>
       <c r="F82" s="24"/>
@@ -2058,8 +2058,8 @@
     </row>
     <row r="83" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="5"/>
-      <c r="B83" s="51"/>
-      <c r="C83" s="52"/>
+      <c r="B83" s="28"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="22"/>
       <c r="E83" s="23"/>
       <c r="F83" s="24"/>
@@ -2069,8 +2069,8 @@
     </row>
     <row r="84" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="5"/>
-      <c r="B84" s="51"/>
-      <c r="C84" s="52"/>
+      <c r="B84" s="28"/>
+      <c r="C84" s="29"/>
       <c r="D84" s="22"/>
       <c r="E84" s="23"/>
       <c r="F84" s="24"/>
@@ -2080,8 +2080,8 @@
     </row>
     <row r="85" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="5"/>
-      <c r="B85" s="51"/>
-      <c r="C85" s="52"/>
+      <c r="B85" s="28"/>
+      <c r="C85" s="29"/>
       <c r="D85" s="22"/>
       <c r="E85" s="23"/>
       <c r="F85" s="24"/>
@@ -2091,8 +2091,8 @@
     </row>
     <row r="86" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="5"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="52"/>
+      <c r="B86" s="28"/>
+      <c r="C86" s="29"/>
       <c r="D86" s="22"/>
       <c r="E86" s="23"/>
       <c r="F86" s="24"/>
@@ -2102,8 +2102,8 @@
     </row>
     <row r="87" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="5"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="52"/>
+      <c r="B87" s="28"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="22"/>
       <c r="E87" s="23"/>
       <c r="F87" s="24"/>
@@ -2113,8 +2113,8 @@
     </row>
     <row r="88" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="5"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="52"/>
+      <c r="B88" s="28"/>
+      <c r="C88" s="29"/>
       <c r="D88" s="22"/>
       <c r="E88" s="23"/>
       <c r="F88" s="24"/>
@@ -2124,8 +2124,8 @@
     </row>
     <row r="89" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="5"/>
-      <c r="B89" s="51"/>
-      <c r="C89" s="52"/>
+      <c r="B89" s="28"/>
+      <c r="C89" s="29"/>
       <c r="D89" s="22"/>
       <c r="E89" s="23"/>
       <c r="F89" s="24"/>
@@ -2135,8 +2135,8 @@
     </row>
     <row r="90" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="5"/>
-      <c r="B90" s="51"/>
-      <c r="C90" s="52"/>
+      <c r="B90" s="28"/>
+      <c r="C90" s="29"/>
       <c r="D90" s="22"/>
       <c r="E90" s="23"/>
       <c r="F90" s="24"/>
@@ -2146,8 +2146,8 @@
     </row>
     <row r="91" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="5"/>
-      <c r="B91" s="51"/>
-      <c r="C91" s="52"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="29"/>
       <c r="D91" s="22"/>
       <c r="E91" s="23"/>
       <c r="F91" s="24"/>
@@ -2157,8 +2157,8 @@
     </row>
     <row r="92" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="5"/>
-      <c r="B92" s="51"/>
-      <c r="C92" s="52"/>
+      <c r="B92" s="28"/>
+      <c r="C92" s="29"/>
       <c r="D92" s="22"/>
       <c r="E92" s="23"/>
       <c r="F92" s="24"/>
@@ -2168,8 +2168,8 @@
     </row>
     <row r="93" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="5"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="52"/>
+      <c r="B93" s="28"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="22"/>
       <c r="E93" s="23"/>
       <c r="F93" s="24"/>
@@ -2179,8 +2179,8 @@
     </row>
     <row r="94" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="5"/>
-      <c r="B94" s="51"/>
-      <c r="C94" s="52"/>
+      <c r="B94" s="28"/>
+      <c r="C94" s="29"/>
       <c r="D94" s="22"/>
       <c r="E94" s="23"/>
       <c r="F94" s="24"/>
@@ -2190,8 +2190,8 @@
     </row>
     <row r="95" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="5"/>
-      <c r="B95" s="51"/>
-      <c r="C95" s="52"/>
+      <c r="B95" s="28"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="22"/>
       <c r="E95" s="23"/>
       <c r="F95" s="24"/>
@@ -2201,8 +2201,8 @@
     </row>
     <row r="96" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="5"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="52"/>
+      <c r="B96" s="28"/>
+      <c r="C96" s="29"/>
       <c r="D96" s="22"/>
       <c r="E96" s="23"/>
       <c r="F96" s="24"/>
@@ -2212,8 +2212,8 @@
     </row>
     <row r="97" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="5"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="52"/>
+      <c r="B97" s="28"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="22"/>
       <c r="E97" s="23"/>
       <c r="F97" s="24"/>
@@ -2223,8 +2223,8 @@
     </row>
     <row r="98" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="5"/>
-      <c r="B98" s="51"/>
-      <c r="C98" s="52"/>
+      <c r="B98" s="28"/>
+      <c r="C98" s="29"/>
       <c r="D98" s="22"/>
       <c r="E98" s="23"/>
       <c r="F98" s="24"/>
@@ -2234,8 +2234,8 @@
     </row>
     <row r="99" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="5"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="52"/>
+      <c r="B99" s="28"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="22"/>
       <c r="E99" s="23"/>
       <c r="F99" s="24"/>
@@ -2245,8 +2245,8 @@
     </row>
     <row r="100" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="5"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="52"/>
+      <c r="B100" s="28"/>
+      <c r="C100" s="29"/>
       <c r="D100" s="22"/>
       <c r="E100" s="23"/>
       <c r="F100" s="24"/>
@@ -2256,8 +2256,8 @@
     </row>
     <row r="101" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="5"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="52"/>
+      <c r="B101" s="28"/>
+      <c r="C101" s="29"/>
       <c r="D101" s="22"/>
       <c r="E101" s="23"/>
       <c r="F101" s="24"/>
@@ -2267,8 +2267,8 @@
     </row>
     <row r="102" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="5"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="52"/>
+      <c r="B102" s="28"/>
+      <c r="C102" s="29"/>
       <c r="D102" s="22"/>
       <c r="E102" s="23"/>
       <c r="F102" s="24"/>
@@ -2278,8 +2278,8 @@
     </row>
     <row r="103" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="5"/>
-      <c r="B103" s="51"/>
-      <c r="C103" s="52"/>
+      <c r="B103" s="28"/>
+      <c r="C103" s="29"/>
       <c r="D103" s="22"/>
       <c r="E103" s="23"/>
       <c r="F103" s="24"/>
@@ -2289,8 +2289,8 @@
     </row>
     <row r="104" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="5"/>
-      <c r="B104" s="51"/>
-      <c r="C104" s="52"/>
+      <c r="B104" s="28"/>
+      <c r="C104" s="29"/>
       <c r="D104" s="22"/>
       <c r="E104" s="23"/>
       <c r="F104" s="24"/>
@@ -2300,8 +2300,8 @@
     </row>
     <row r="105" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="5"/>
-      <c r="B105" s="51"/>
-      <c r="C105" s="52"/>
+      <c r="B105" s="28"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="22"/>
       <c r="E105" s="23"/>
       <c r="F105" s="24"/>
@@ -2311,8 +2311,8 @@
     </row>
     <row r="106" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="5"/>
-      <c r="B106" s="51"/>
-      <c r="C106" s="52"/>
+      <c r="B106" s="28"/>
+      <c r="C106" s="29"/>
       <c r="D106" s="22"/>
       <c r="E106" s="23"/>
       <c r="F106" s="24"/>
@@ -2322,8 +2322,8 @@
     </row>
     <row r="107" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="5"/>
-      <c r="B107" s="51"/>
-      <c r="C107" s="52"/>
+      <c r="B107" s="28"/>
+      <c r="C107" s="29"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
@@ -2333,8 +2333,8 @@
     </row>
     <row r="108" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="5"/>
-      <c r="B108" s="51"/>
-      <c r="C108" s="52"/>
+      <c r="B108" s="28"/>
+      <c r="C108" s="29"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
@@ -2344,8 +2344,8 @@
     </row>
     <row r="109" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="5"/>
-      <c r="B109" s="51"/>
-      <c r="C109" s="52"/>
+      <c r="B109" s="28"/>
+      <c r="C109" s="29"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
@@ -2355,8 +2355,8 @@
     </row>
     <row r="110" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="5"/>
-      <c r="B110" s="51"/>
-      <c r="C110" s="52"/>
+      <c r="B110" s="28"/>
+      <c r="C110" s="29"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
@@ -2366,8 +2366,8 @@
     </row>
     <row r="111" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="5"/>
-      <c r="B111" s="51"/>
-      <c r="C111" s="52"/>
+      <c r="B111" s="28"/>
+      <c r="C111" s="29"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
@@ -2377,8 +2377,8 @@
     </row>
     <row r="112" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="5"/>
-      <c r="B112" s="51"/>
-      <c r="C112" s="52"/>
+      <c r="B112" s="28"/>
+      <c r="C112" s="29"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
@@ -2388,8 +2388,8 @@
     </row>
     <row r="113" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="5"/>
-      <c r="B113" s="51"/>
-      <c r="C113" s="52"/>
+      <c r="B113" s="28"/>
+      <c r="C113" s="29"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
@@ -2399,8 +2399,8 @@
     </row>
     <row r="114" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="5"/>
-      <c r="B114" s="51"/>
-      <c r="C114" s="52"/>
+      <c r="B114" s="28"/>
+      <c r="C114" s="29"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
@@ -2410,8 +2410,8 @@
     </row>
     <row r="115" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5"/>
-      <c r="B115" s="51"/>
-      <c r="C115" s="52"/>
+      <c r="B115" s="28"/>
+      <c r="C115" s="29"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
@@ -2421,8 +2421,8 @@
     </row>
     <row r="116" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5"/>
-      <c r="B116" s="51"/>
-      <c r="C116" s="52"/>
+      <c r="B116" s="28"/>
+      <c r="C116" s="29"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -2432,8 +2432,8 @@
     </row>
     <row r="117" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="5"/>
-      <c r="B117" s="51"/>
-      <c r="C117" s="52"/>
+      <c r="B117" s="28"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -2443,8 +2443,8 @@
     </row>
     <row r="118" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="5"/>
-      <c r="B118" s="51"/>
-      <c r="C118" s="52"/>
+      <c r="B118" s="28"/>
+      <c r="C118" s="29"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -2454,8 +2454,8 @@
     </row>
     <row r="119" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="5"/>
-      <c r="B119" s="51"/>
-      <c r="C119" s="52"/>
+      <c r="B119" s="28"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -2465,8 +2465,8 @@
     </row>
     <row r="120" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="5"/>
-      <c r="B120" s="51"/>
-      <c r="C120" s="52"/>
+      <c r="B120" s="28"/>
+      <c r="C120" s="29"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -2476,8 +2476,8 @@
     </row>
     <row r="121" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="5"/>
-      <c r="B121" s="51"/>
-      <c r="C121" s="52"/>
+      <c r="B121" s="28"/>
+      <c r="C121" s="29"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -2487,8 +2487,8 @@
     </row>
     <row r="122" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="5"/>
-      <c r="B122" s="51"/>
-      <c r="C122" s="52"/>
+      <c r="B122" s="28"/>
+      <c r="C122" s="29"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -2498,8 +2498,8 @@
     </row>
     <row r="123" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="5"/>
-      <c r="B123" s="51"/>
-      <c r="C123" s="52"/>
+      <c r="B123" s="28"/>
+      <c r="C123" s="29"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -2509,8 +2509,8 @@
     </row>
     <row r="124" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5"/>
-      <c r="B124" s="51"/>
-      <c r="C124" s="52"/>
+      <c r="B124" s="28"/>
+      <c r="C124" s="29"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -2520,8 +2520,8 @@
     </row>
     <row r="125" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5"/>
-      <c r="B125" s="51"/>
-      <c r="C125" s="52"/>
+      <c r="B125" s="28"/>
+      <c r="C125" s="29"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -2531,8 +2531,8 @@
     </row>
     <row r="126" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5"/>
-      <c r="B126" s="51"/>
-      <c r="C126" s="52"/>
+      <c r="B126" s="28"/>
+      <c r="C126" s="29"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -2542,8 +2542,8 @@
     </row>
     <row r="127" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5"/>
-      <c r="B127" s="51"/>
-      <c r="C127" s="52"/>
+      <c r="B127" s="28"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -2553,8 +2553,8 @@
     </row>
     <row r="128" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5"/>
-      <c r="B128" s="51"/>
-      <c r="C128" s="52"/>
+      <c r="B128" s="28"/>
+      <c r="C128" s="29"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -2564,8 +2564,8 @@
     </row>
     <row r="129" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="5"/>
-      <c r="B129" s="51"/>
-      <c r="C129" s="52"/>
+      <c r="B129" s="28"/>
+      <c r="C129" s="29"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -2575,8 +2575,8 @@
     </row>
     <row r="130" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="5"/>
-      <c r="B130" s="51"/>
-      <c r="C130" s="52"/>
+      <c r="B130" s="28"/>
+      <c r="C130" s="29"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -2586,8 +2586,8 @@
     </row>
     <row r="131" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="5"/>
-      <c r="B131" s="51"/>
-      <c r="C131" s="52"/>
+      <c r="B131" s="28"/>
+      <c r="C131" s="29"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -2597,8 +2597,8 @@
     </row>
     <row r="132" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="5"/>
-      <c r="B132" s="51"/>
-      <c r="C132" s="52"/>
+      <c r="B132" s="28"/>
+      <c r="C132" s="29"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -2608,8 +2608,8 @@
     </row>
     <row r="133" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5"/>
-      <c r="B133" s="51"/>
-      <c r="C133" s="52"/>
+      <c r="B133" s="28"/>
+      <c r="C133" s="29"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -2619,8 +2619,8 @@
     </row>
     <row r="134" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="5"/>
-      <c r="B134" s="51"/>
-      <c r="C134" s="52"/>
+      <c r="B134" s="28"/>
+      <c r="C134" s="29"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -2630,8 +2630,8 @@
     </row>
     <row r="135" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="5"/>
-      <c r="B135" s="51"/>
-      <c r="C135" s="52"/>
+      <c r="B135" s="28"/>
+      <c r="C135" s="29"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -2641,8 +2641,8 @@
     </row>
     <row r="136" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="5"/>
-      <c r="B136" s="51"/>
-      <c r="C136" s="52"/>
+      <c r="B136" s="28"/>
+      <c r="C136" s="29"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -2652,8 +2652,8 @@
     </row>
     <row r="137" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="5"/>
-      <c r="B137" s="51"/>
-      <c r="C137" s="52"/>
+      <c r="B137" s="28"/>
+      <c r="C137" s="29"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -2663,8 +2663,8 @@
     </row>
     <row r="138" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="5"/>
-      <c r="B138" s="51"/>
-      <c r="C138" s="52"/>
+      <c r="B138" s="28"/>
+      <c r="C138" s="29"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -2674,8 +2674,8 @@
     </row>
     <row r="139" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="5"/>
-      <c r="B139" s="51"/>
-      <c r="C139" s="52"/>
+      <c r="B139" s="28"/>
+      <c r="C139" s="29"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
@@ -2685,8 +2685,8 @@
     </row>
     <row r="140" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="5"/>
-      <c r="B140" s="51"/>
-      <c r="C140" s="52"/>
+      <c r="B140" s="28"/>
+      <c r="C140" s="29"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -2696,8 +2696,8 @@
     </row>
     <row r="141" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="5"/>
-      <c r="B141" s="51"/>
-      <c r="C141" s="52"/>
+      <c r="B141" s="28"/>
+      <c r="C141" s="29"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -2707,8 +2707,8 @@
     </row>
     <row r="142" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="5"/>
-      <c r="B142" s="51"/>
-      <c r="C142" s="52"/>
+      <c r="B142" s="28"/>
+      <c r="C142" s="29"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -2718,8 +2718,8 @@
     </row>
     <row r="143" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="5"/>
-      <c r="B143" s="51"/>
-      <c r="C143" s="52"/>
+      <c r="B143" s="28"/>
+      <c r="C143" s="29"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -2729,8 +2729,8 @@
     </row>
     <row r="144" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="5"/>
-      <c r="B144" s="51"/>
-      <c r="C144" s="52"/>
+      <c r="B144" s="28"/>
+      <c r="C144" s="29"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -2740,8 +2740,8 @@
     </row>
     <row r="145" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="5"/>
-      <c r="B145" s="51"/>
-      <c r="C145" s="52"/>
+      <c r="B145" s="28"/>
+      <c r="C145" s="29"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -2751,8 +2751,8 @@
     </row>
     <row r="146" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="5"/>
-      <c r="B146" s="51"/>
-      <c r="C146" s="52"/>
+      <c r="B146" s="28"/>
+      <c r="C146" s="29"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -2762,8 +2762,8 @@
     </row>
     <row r="147" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="5"/>
-      <c r="B147" s="51"/>
-      <c r="C147" s="52"/>
+      <c r="B147" s="28"/>
+      <c r="C147" s="29"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -2773,8 +2773,8 @@
     </row>
     <row r="148" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="5"/>
-      <c r="B148" s="51"/>
-      <c r="C148" s="52"/>
+      <c r="B148" s="28"/>
+      <c r="C148" s="29"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -2784,8 +2784,8 @@
     </row>
     <row r="149" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="5"/>
-      <c r="B149" s="51"/>
-      <c r="C149" s="52"/>
+      <c r="B149" s="28"/>
+      <c r="C149" s="29"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -2795,8 +2795,8 @@
     </row>
     <row r="150" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="5"/>
-      <c r="B150" s="51"/>
-      <c r="C150" s="52"/>
+      <c r="B150" s="28"/>
+      <c r="C150" s="29"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -2806,126 +2806,26 @@
     </row>
   </sheetData>
   <mergeCells count="164">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="H1:I2"/>
+    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="H3:I4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
@@ -2950,26 +2850,126 @@
     <mergeCell ref="B129:C129"/>
     <mergeCell ref="B130:C130"/>
     <mergeCell ref="B131:C131"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="H1:I2"/>
-    <mergeCell ref="D2:E3"/>
-    <mergeCell ref="H3:I4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/documents_bin/1818图册目录模板.xlsx
+++ b/documents_bin/1818图册目录模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project\auto-fanban-pre\documents_bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956CAF17-E768-4729-B251-1927D0BD0432}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AF0724-7E66-4B0A-8D28-1E02AF9FABB5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>文件编号:</t>
-  </si>
-  <si>
-    <t>第  图册图纸（文件)目录</t>
   </si>
   <si>
     <t>Document Code</t>
@@ -287,6 +284,10 @@
       </rPr>
       <t>Remarks</t>
     </r>
+  </si>
+  <si>
+    <t>图纸（文件)目录</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -649,82 +650,82 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1059,21 +1060,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="44"/>
       <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50" t="s">
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="43"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
@@ -1081,108 +1082,108 @@
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="51" t="s">
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="45"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="52" t="s">
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="52"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="45"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A4" s="13"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="42"/>
+      <c r="F4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="52" t="s">
+      <c r="G4" s="48"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
+    </row>
+    <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="52"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="45"/>
-    </row>
-    <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="53" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="46" t="s">
+      <c r="E5" s="42"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="32"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.15">
+      <c r="A6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A6" s="17" t="s">
-        <v>11</v>
-      </c>
       <c r="B6" s="18"/>
-      <c r="C6" s="33"/>
+      <c r="C6" s="53"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="15"/>
       <c r="G6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="33"/>
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:28" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="21"/>
-    </row>
-    <row r="7" spans="1:28" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="30" t="s">
+      <c r="B7" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="C7" s="35"/>
+      <c r="D7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="30" t="s">
+      <c r="E7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="F7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="G7" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="H7" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="I7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="30" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A8" s="31"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="H8" s="31"/>
@@ -1190,8 +1191,8 @@
     </row>
     <row r="9" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="22"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
@@ -1201,8 +1202,8 @@
     </row>
     <row r="10" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="52"/>
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -1212,8 +1213,8 @@
     </row>
     <row r="11" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="22"/>
       <c r="E11" s="23"/>
       <c r="F11" s="24"/>
@@ -1223,8 +1224,8 @@
     </row>
     <row r="12" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="52"/>
       <c r="D12" s="22"/>
       <c r="E12" s="23"/>
       <c r="F12" s="24"/>
@@ -1234,8 +1235,8 @@
     </row>
     <row r="13" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="22"/>
       <c r="E13" s="23"/>
       <c r="F13" s="24"/>
@@ -1245,8 +1246,8 @@
     </row>
     <row r="14" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="22"/>
       <c r="E14" s="23"/>
       <c r="F14" s="24"/>
@@ -1273,8 +1274,8 @@
       <c r="AB14" s="26"/>
     </row>
     <row r="15" spans="1:28" s="5" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
       <c r="D15" s="22"/>
       <c r="E15" s="23"/>
       <c r="F15" s="24"/>
@@ -1303,8 +1304,8 @@
     </row>
     <row r="16" spans="1:28" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="22"/>
       <c r="E16" s="23"/>
       <c r="F16" s="24"/>
@@ -1332,8 +1333,8 @@
     </row>
     <row r="17" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="22"/>
       <c r="E17" s="23"/>
       <c r="F17" s="24"/>
@@ -1343,8 +1344,8 @@
     </row>
     <row r="18" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="22"/>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -1354,8 +1355,8 @@
     </row>
     <row r="19" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="22"/>
       <c r="E19" s="23"/>
       <c r="F19" s="24"/>
@@ -1365,8 +1366,8 @@
     </row>
     <row r="20" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="22"/>
       <c r="E20" s="23"/>
       <c r="F20" s="24"/>
@@ -1376,8 +1377,8 @@
     </row>
     <row r="21" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="22"/>
       <c r="E21" s="23"/>
       <c r="F21" s="24"/>
@@ -1387,8 +1388,8 @@
     </row>
     <row r="22" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="22"/>
       <c r="E22" s="23"/>
       <c r="F22" s="24"/>
@@ -1398,8 +1399,8 @@
     </row>
     <row r="23" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="22"/>
       <c r="E23" s="23"/>
       <c r="F23" s="24"/>
@@ -1409,8 +1410,8 @@
     </row>
     <row r="24" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="22"/>
       <c r="E24" s="23"/>
       <c r="F24" s="24"/>
@@ -1420,8 +1421,8 @@
     </row>
     <row r="25" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="22"/>
       <c r="E25" s="23"/>
       <c r="F25" s="24"/>
@@ -1431,8 +1432,8 @@
     </row>
     <row r="26" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="22"/>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -1442,8 +1443,8 @@
     </row>
     <row r="27" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="22"/>
       <c r="E27" s="23"/>
       <c r="F27" s="24"/>
@@ -1453,8 +1454,8 @@
     </row>
     <row r="28" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="22"/>
       <c r="E28" s="23"/>
       <c r="F28" s="24"/>
@@ -1464,8 +1465,8 @@
     </row>
     <row r="29" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="22"/>
       <c r="E29" s="23"/>
       <c r="F29" s="24"/>
@@ -1475,8 +1476,8 @@
     </row>
     <row r="30" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
       <c r="D30" s="22"/>
       <c r="E30" s="23"/>
       <c r="F30" s="24"/>
@@ -1486,8 +1487,8 @@
     </row>
     <row r="31" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="52"/>
       <c r="D31" s="22"/>
       <c r="E31" s="23"/>
       <c r="F31" s="24"/>
@@ -1497,8 +1498,8 @@
     </row>
     <row r="32" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="22"/>
       <c r="E32" s="23"/>
       <c r="F32" s="24"/>
@@ -1508,8 +1509,8 @@
     </row>
     <row r="33" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="22"/>
       <c r="E33" s="23"/>
       <c r="F33" s="24"/>
@@ -1519,8 +1520,8 @@
     </row>
     <row r="34" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="29"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="22"/>
       <c r="E34" s="23"/>
       <c r="F34" s="24"/>
@@ -1530,8 +1531,8 @@
     </row>
     <row r="35" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="29"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="52"/>
       <c r="D35" s="22"/>
       <c r="E35" s="23"/>
       <c r="F35" s="24"/>
@@ -1541,8 +1542,8 @@
     </row>
     <row r="36" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="29"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="22"/>
       <c r="E36" s="23"/>
       <c r="F36" s="24"/>
@@ -1552,8 +1553,8 @@
     </row>
     <row r="37" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="29"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="22"/>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
@@ -1563,8 +1564,8 @@
     </row>
     <row r="38" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="29"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
       <c r="D38" s="22"/>
       <c r="E38" s="23"/>
       <c r="F38" s="24"/>
@@ -1574,8 +1575,8 @@
     </row>
     <row r="39" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="29"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="52"/>
       <c r="D39" s="22"/>
       <c r="E39" s="23"/>
       <c r="F39" s="24"/>
@@ -1585,8 +1586,8 @@
     </row>
     <row r="40" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="29"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
       <c r="D40" s="22"/>
       <c r="E40" s="23"/>
       <c r="F40" s="24"/>
@@ -1596,8 +1597,8 @@
     </row>
     <row r="41" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="52"/>
       <c r="D41" s="22"/>
       <c r="E41" s="23"/>
       <c r="F41" s="24"/>
@@ -1607,8 +1608,8 @@
     </row>
     <row r="42" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="29"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
       <c r="D42" s="22"/>
       <c r="E42" s="23"/>
       <c r="F42" s="24"/>
@@ -1618,8 +1619,8 @@
     </row>
     <row r="43" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="5"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="52"/>
       <c r="D43" s="22"/>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
@@ -1629,8 +1630,8 @@
     </row>
     <row r="44" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="29"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
       <c r="D44" s="22"/>
       <c r="E44" s="23"/>
       <c r="F44" s="24"/>
@@ -1640,8 +1641,8 @@
     </row>
     <row r="45" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="29"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="52"/>
       <c r="D45" s="22"/>
       <c r="E45" s="23"/>
       <c r="F45" s="24"/>
@@ -1651,8 +1652,8 @@
     </row>
     <row r="46" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="29"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
       <c r="D46" s="22"/>
       <c r="E46" s="23"/>
       <c r="F46" s="24"/>
@@ -1662,8 +1663,8 @@
     </row>
     <row r="47" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="5"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="29"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="22"/>
       <c r="E47" s="23"/>
       <c r="F47" s="24"/>
@@ -1673,8 +1674,8 @@
     </row>
     <row r="48" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="5"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="29"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="22"/>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
@@ -1684,8 +1685,8 @@
     </row>
     <row r="49" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="5"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="29"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="22"/>
       <c r="E49" s="23"/>
       <c r="F49" s="24"/>
@@ -1695,8 +1696,8 @@
     </row>
     <row r="50" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="5"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="29"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="52"/>
       <c r="D50" s="22"/>
       <c r="E50" s="23"/>
       <c r="F50" s="24"/>
@@ -1706,8 +1707,8 @@
     </row>
     <row r="51" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="29"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="52"/>
       <c r="D51" s="22"/>
       <c r="E51" s="23"/>
       <c r="F51" s="24"/>
@@ -1717,8 +1718,8 @@
     </row>
     <row r="52" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="5"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="29"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="22"/>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
@@ -1728,8 +1729,8 @@
     </row>
     <row r="53" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="29"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="22"/>
       <c r="E53" s="23"/>
       <c r="F53" s="24"/>
@@ -1739,8 +1740,8 @@
     </row>
     <row r="54" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="5"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="29"/>
+      <c r="B54" s="51"/>
+      <c r="C54" s="52"/>
       <c r="D54" s="22"/>
       <c r="E54" s="23"/>
       <c r="F54" s="24"/>
@@ -1750,8 +1751,8 @@
     </row>
     <row r="55" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="5"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="29"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="22"/>
       <c r="E55" s="23"/>
       <c r="F55" s="24"/>
@@ -1761,8 +1762,8 @@
     </row>
     <row r="56" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="5"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="29"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="22"/>
       <c r="E56" s="23"/>
       <c r="F56" s="24"/>
@@ -1772,8 +1773,8 @@
     </row>
     <row r="57" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="5"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="29"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="52"/>
       <c r="D57" s="22"/>
       <c r="E57" s="23"/>
       <c r="F57" s="24"/>
@@ -1783,8 +1784,8 @@
     </row>
     <row r="58" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="5"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="29"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="22"/>
       <c r="E58" s="23"/>
       <c r="F58" s="24"/>
@@ -1794,8 +1795,8 @@
     </row>
     <row r="59" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="5"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="29"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="52"/>
       <c r="D59" s="22"/>
       <c r="E59" s="23"/>
       <c r="F59" s="24"/>
@@ -1805,8 +1806,8 @@
     </row>
     <row r="60" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="5"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="29"/>
+      <c r="B60" s="51"/>
+      <c r="C60" s="52"/>
       <c r="D60" s="22"/>
       <c r="E60" s="23"/>
       <c r="F60" s="24"/>
@@ -1816,8 +1817,8 @@
     </row>
     <row r="61" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="5"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="29"/>
+      <c r="B61" s="51"/>
+      <c r="C61" s="52"/>
       <c r="D61" s="22"/>
       <c r="E61" s="23"/>
       <c r="F61" s="24"/>
@@ -1827,8 +1828,8 @@
     </row>
     <row r="62" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="5"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="29"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="52"/>
       <c r="D62" s="22"/>
       <c r="E62" s="23"/>
       <c r="F62" s="24"/>
@@ -1838,8 +1839,8 @@
     </row>
     <row r="63" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="5"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="29"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="52"/>
       <c r="D63" s="22"/>
       <c r="E63" s="23"/>
       <c r="F63" s="24"/>
@@ -1849,8 +1850,8 @@
     </row>
     <row r="64" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="5"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="29"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="52"/>
       <c r="D64" s="22"/>
       <c r="E64" s="23"/>
       <c r="F64" s="24"/>
@@ -1860,8 +1861,8 @@
     </row>
     <row r="65" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="5"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="29"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="52"/>
       <c r="D65" s="22"/>
       <c r="E65" s="23"/>
       <c r="F65" s="24"/>
@@ -1871,8 +1872,8 @@
     </row>
     <row r="66" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="5"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="29"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="52"/>
       <c r="D66" s="22"/>
       <c r="E66" s="23"/>
       <c r="F66" s="24"/>
@@ -1882,8 +1883,8 @@
     </row>
     <row r="67" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="5"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="29"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="52"/>
       <c r="D67" s="22"/>
       <c r="E67" s="23"/>
       <c r="F67" s="24"/>
@@ -1893,8 +1894,8 @@
     </row>
     <row r="68" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="5"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="29"/>
+      <c r="B68" s="51"/>
+      <c r="C68" s="52"/>
       <c r="D68" s="22"/>
       <c r="E68" s="23"/>
       <c r="F68" s="24"/>
@@ -1904,8 +1905,8 @@
     </row>
     <row r="69" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="5"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="29"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="52"/>
       <c r="D69" s="22"/>
       <c r="E69" s="23"/>
       <c r="F69" s="24"/>
@@ -1915,8 +1916,8 @@
     </row>
     <row r="70" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="5"/>
-      <c r="B70" s="28"/>
-      <c r="C70" s="29"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="52"/>
       <c r="D70" s="22"/>
       <c r="E70" s="23"/>
       <c r="F70" s="24"/>
@@ -1926,8 +1927,8 @@
     </row>
     <row r="71" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="5"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="29"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="52"/>
       <c r="D71" s="22"/>
       <c r="E71" s="23"/>
       <c r="F71" s="24"/>
@@ -1937,8 +1938,8 @@
     </row>
     <row r="72" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="5"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="29"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="52"/>
       <c r="D72" s="22"/>
       <c r="E72" s="23"/>
       <c r="F72" s="24"/>
@@ -1948,8 +1949,8 @@
     </row>
     <row r="73" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="5"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="29"/>
+      <c r="B73" s="51"/>
+      <c r="C73" s="52"/>
       <c r="D73" s="22"/>
       <c r="E73" s="23"/>
       <c r="F73" s="24"/>
@@ -1959,8 +1960,8 @@
     </row>
     <row r="74" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="5"/>
-      <c r="B74" s="28"/>
-      <c r="C74" s="29"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="52"/>
       <c r="D74" s="22"/>
       <c r="E74" s="23"/>
       <c r="F74" s="24"/>
@@ -1970,8 +1971,8 @@
     </row>
     <row r="75" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="5"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="29"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="52"/>
       <c r="D75" s="22"/>
       <c r="E75" s="23"/>
       <c r="F75" s="24"/>
@@ -1981,8 +1982,8 @@
     </row>
     <row r="76" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="5"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="29"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="52"/>
       <c r="D76" s="22"/>
       <c r="E76" s="23"/>
       <c r="F76" s="24"/>
@@ -1992,8 +1993,8 @@
     </row>
     <row r="77" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="5"/>
-      <c r="B77" s="28"/>
-      <c r="C77" s="29"/>
+      <c r="B77" s="51"/>
+      <c r="C77" s="52"/>
       <c r="D77" s="22"/>
       <c r="E77" s="23"/>
       <c r="F77" s="24"/>
@@ -2003,8 +2004,8 @@
     </row>
     <row r="78" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="5"/>
-      <c r="B78" s="28"/>
-      <c r="C78" s="29"/>
+      <c r="B78" s="51"/>
+      <c r="C78" s="52"/>
       <c r="D78" s="22"/>
       <c r="E78" s="23"/>
       <c r="F78" s="24"/>
@@ -2014,8 +2015,8 @@
     </row>
     <row r="79" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="5"/>
-      <c r="B79" s="28"/>
-      <c r="C79" s="29"/>
+      <c r="B79" s="51"/>
+      <c r="C79" s="52"/>
       <c r="D79" s="22"/>
       <c r="E79" s="23"/>
       <c r="F79" s="24"/>
@@ -2025,8 +2026,8 @@
     </row>
     <row r="80" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="5"/>
-      <c r="B80" s="28"/>
-      <c r="C80" s="29"/>
+      <c r="B80" s="51"/>
+      <c r="C80" s="52"/>
       <c r="D80" s="22"/>
       <c r="E80" s="23"/>
       <c r="F80" s="24"/>
@@ -2036,8 +2037,8 @@
     </row>
     <row r="81" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="5"/>
-      <c r="B81" s="28"/>
-      <c r="C81" s="29"/>
+      <c r="B81" s="51"/>
+      <c r="C81" s="52"/>
       <c r="D81" s="22"/>
       <c r="E81" s="23"/>
       <c r="F81" s="24"/>
@@ -2047,8 +2048,8 @@
     </row>
     <row r="82" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="5"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="29"/>
+      <c r="B82" s="51"/>
+      <c r="C82" s="52"/>
       <c r="D82" s="22"/>
       <c r="E82" s="23"/>
       <c r="F82" s="24"/>
@@ -2058,8 +2059,8 @@
     </row>
     <row r="83" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="5"/>
-      <c r="B83" s="28"/>
-      <c r="C83" s="29"/>
+      <c r="B83" s="51"/>
+      <c r="C83" s="52"/>
       <c r="D83" s="22"/>
       <c r="E83" s="23"/>
       <c r="F83" s="24"/>
@@ -2069,8 +2070,8 @@
     </row>
     <row r="84" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="5"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="29"/>
+      <c r="B84" s="51"/>
+      <c r="C84" s="52"/>
       <c r="D84" s="22"/>
       <c r="E84" s="23"/>
       <c r="F84" s="24"/>
@@ -2080,8 +2081,8 @@
     </row>
     <row r="85" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="5"/>
-      <c r="B85" s="28"/>
-      <c r="C85" s="29"/>
+      <c r="B85" s="51"/>
+      <c r="C85" s="52"/>
       <c r="D85" s="22"/>
       <c r="E85" s="23"/>
       <c r="F85" s="24"/>
@@ -2091,8 +2092,8 @@
     </row>
     <row r="86" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="5"/>
-      <c r="B86" s="28"/>
-      <c r="C86" s="29"/>
+      <c r="B86" s="51"/>
+      <c r="C86" s="52"/>
       <c r="D86" s="22"/>
       <c r="E86" s="23"/>
       <c r="F86" s="24"/>
@@ -2102,8 +2103,8 @@
     </row>
     <row r="87" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="5"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="29"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="52"/>
       <c r="D87" s="22"/>
       <c r="E87" s="23"/>
       <c r="F87" s="24"/>
@@ -2113,8 +2114,8 @@
     </row>
     <row r="88" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="5"/>
-      <c r="B88" s="28"/>
-      <c r="C88" s="29"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="52"/>
       <c r="D88" s="22"/>
       <c r="E88" s="23"/>
       <c r="F88" s="24"/>
@@ -2124,8 +2125,8 @@
     </row>
     <row r="89" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="5"/>
-      <c r="B89" s="28"/>
-      <c r="C89" s="29"/>
+      <c r="B89" s="51"/>
+      <c r="C89" s="52"/>
       <c r="D89" s="22"/>
       <c r="E89" s="23"/>
       <c r="F89" s="24"/>
@@ -2135,8 +2136,8 @@
     </row>
     <row r="90" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="5"/>
-      <c r="B90" s="28"/>
-      <c r="C90" s="29"/>
+      <c r="B90" s="51"/>
+      <c r="C90" s="52"/>
       <c r="D90" s="22"/>
       <c r="E90" s="23"/>
       <c r="F90" s="24"/>
@@ -2146,8 +2147,8 @@
     </row>
     <row r="91" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="5"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="29"/>
+      <c r="B91" s="51"/>
+      <c r="C91" s="52"/>
       <c r="D91" s="22"/>
       <c r="E91" s="23"/>
       <c r="F91" s="24"/>
@@ -2157,8 +2158,8 @@
     </row>
     <row r="92" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="5"/>
-      <c r="B92" s="28"/>
-      <c r="C92" s="29"/>
+      <c r="B92" s="51"/>
+      <c r="C92" s="52"/>
       <c r="D92" s="22"/>
       <c r="E92" s="23"/>
       <c r="F92" s="24"/>
@@ -2168,8 +2169,8 @@
     </row>
     <row r="93" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="5"/>
-      <c r="B93" s="28"/>
-      <c r="C93" s="29"/>
+      <c r="B93" s="51"/>
+      <c r="C93" s="52"/>
       <c r="D93" s="22"/>
       <c r="E93" s="23"/>
       <c r="F93" s="24"/>
@@ -2179,8 +2180,8 @@
     </row>
     <row r="94" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="5"/>
-      <c r="B94" s="28"/>
-      <c r="C94" s="29"/>
+      <c r="B94" s="51"/>
+      <c r="C94" s="52"/>
       <c r="D94" s="22"/>
       <c r="E94" s="23"/>
       <c r="F94" s="24"/>
@@ -2190,8 +2191,8 @@
     </row>
     <row r="95" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="5"/>
-      <c r="B95" s="28"/>
-      <c r="C95" s="29"/>
+      <c r="B95" s="51"/>
+      <c r="C95" s="52"/>
       <c r="D95" s="22"/>
       <c r="E95" s="23"/>
       <c r="F95" s="24"/>
@@ -2201,8 +2202,8 @@
     </row>
     <row r="96" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="5"/>
-      <c r="B96" s="28"/>
-      <c r="C96" s="29"/>
+      <c r="B96" s="51"/>
+      <c r="C96" s="52"/>
       <c r="D96" s="22"/>
       <c r="E96" s="23"/>
       <c r="F96" s="24"/>
@@ -2212,8 +2213,8 @@
     </row>
     <row r="97" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="5"/>
-      <c r="B97" s="28"/>
-      <c r="C97" s="29"/>
+      <c r="B97" s="51"/>
+      <c r="C97" s="52"/>
       <c r="D97" s="22"/>
       <c r="E97" s="23"/>
       <c r="F97" s="24"/>
@@ -2223,8 +2224,8 @@
     </row>
     <row r="98" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="5"/>
-      <c r="B98" s="28"/>
-      <c r="C98" s="29"/>
+      <c r="B98" s="51"/>
+      <c r="C98" s="52"/>
       <c r="D98" s="22"/>
       <c r="E98" s="23"/>
       <c r="F98" s="24"/>
@@ -2234,8 +2235,8 @@
     </row>
     <row r="99" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="5"/>
-      <c r="B99" s="28"/>
-      <c r="C99" s="29"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="52"/>
       <c r="D99" s="22"/>
       <c r="E99" s="23"/>
       <c r="F99" s="24"/>
@@ -2245,8 +2246,8 @@
     </row>
     <row r="100" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="5"/>
-      <c r="B100" s="28"/>
-      <c r="C100" s="29"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="52"/>
       <c r="D100" s="22"/>
       <c r="E100" s="23"/>
       <c r="F100" s="24"/>
@@ -2256,8 +2257,8 @@
     </row>
     <row r="101" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="5"/>
-      <c r="B101" s="28"/>
-      <c r="C101" s="29"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="52"/>
       <c r="D101" s="22"/>
       <c r="E101" s="23"/>
       <c r="F101" s="24"/>
@@ -2267,8 +2268,8 @@
     </row>
     <row r="102" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="5"/>
-      <c r="B102" s="28"/>
-      <c r="C102" s="29"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="52"/>
       <c r="D102" s="22"/>
       <c r="E102" s="23"/>
       <c r="F102" s="24"/>
@@ -2278,8 +2279,8 @@
     </row>
     <row r="103" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="5"/>
-      <c r="B103" s="28"/>
-      <c r="C103" s="29"/>
+      <c r="B103" s="51"/>
+      <c r="C103" s="52"/>
       <c r="D103" s="22"/>
       <c r="E103" s="23"/>
       <c r="F103" s="24"/>
@@ -2289,8 +2290,8 @@
     </row>
     <row r="104" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="5"/>
-      <c r="B104" s="28"/>
-      <c r="C104" s="29"/>
+      <c r="B104" s="51"/>
+      <c r="C104" s="52"/>
       <c r="D104" s="22"/>
       <c r="E104" s="23"/>
       <c r="F104" s="24"/>
@@ -2300,8 +2301,8 @@
     </row>
     <row r="105" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="5"/>
-      <c r="B105" s="28"/>
-      <c r="C105" s="29"/>
+      <c r="B105" s="51"/>
+      <c r="C105" s="52"/>
       <c r="D105" s="22"/>
       <c r="E105" s="23"/>
       <c r="F105" s="24"/>
@@ -2311,8 +2312,8 @@
     </row>
     <row r="106" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="5"/>
-      <c r="B106" s="28"/>
-      <c r="C106" s="29"/>
+      <c r="B106" s="51"/>
+      <c r="C106" s="52"/>
       <c r="D106" s="22"/>
       <c r="E106" s="23"/>
       <c r="F106" s="24"/>
@@ -2322,8 +2323,8 @@
     </row>
     <row r="107" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="5"/>
-      <c r="B107" s="28"/>
-      <c r="C107" s="29"/>
+      <c r="B107" s="51"/>
+      <c r="C107" s="52"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
@@ -2333,8 +2334,8 @@
     </row>
     <row r="108" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="5"/>
-      <c r="B108" s="28"/>
-      <c r="C108" s="29"/>
+      <c r="B108" s="51"/>
+      <c r="C108" s="52"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
@@ -2344,8 +2345,8 @@
     </row>
     <row r="109" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="5"/>
-      <c r="B109" s="28"/>
-      <c r="C109" s="29"/>
+      <c r="B109" s="51"/>
+      <c r="C109" s="52"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
@@ -2355,8 +2356,8 @@
     </row>
     <row r="110" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="5"/>
-      <c r="B110" s="28"/>
-      <c r="C110" s="29"/>
+      <c r="B110" s="51"/>
+      <c r="C110" s="52"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
@@ -2366,8 +2367,8 @@
     </row>
     <row r="111" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="5"/>
-      <c r="B111" s="28"/>
-      <c r="C111" s="29"/>
+      <c r="B111" s="51"/>
+      <c r="C111" s="52"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
@@ -2377,8 +2378,8 @@
     </row>
     <row r="112" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="5"/>
-      <c r="B112" s="28"/>
-      <c r="C112" s="29"/>
+      <c r="B112" s="51"/>
+      <c r="C112" s="52"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
@@ -2388,8 +2389,8 @@
     </row>
     <row r="113" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="5"/>
-      <c r="B113" s="28"/>
-      <c r="C113" s="29"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="52"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
@@ -2399,8 +2400,8 @@
     </row>
     <row r="114" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="5"/>
-      <c r="B114" s="28"/>
-      <c r="C114" s="29"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="52"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
@@ -2410,8 +2411,8 @@
     </row>
     <row r="115" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5"/>
-      <c r="B115" s="28"/>
-      <c r="C115" s="29"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="52"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
@@ -2421,8 +2422,8 @@
     </row>
     <row r="116" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5"/>
-      <c r="B116" s="28"/>
-      <c r="C116" s="29"/>
+      <c r="B116" s="51"/>
+      <c r="C116" s="52"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -2432,8 +2433,8 @@
     </row>
     <row r="117" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="5"/>
-      <c r="B117" s="28"/>
-      <c r="C117" s="29"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="52"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -2443,8 +2444,8 @@
     </row>
     <row r="118" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="5"/>
-      <c r="B118" s="28"/>
-      <c r="C118" s="29"/>
+      <c r="B118" s="51"/>
+      <c r="C118" s="52"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -2454,8 +2455,8 @@
     </row>
     <row r="119" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="5"/>
-      <c r="B119" s="28"/>
-      <c r="C119" s="29"/>
+      <c r="B119" s="51"/>
+      <c r="C119" s="52"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -2465,8 +2466,8 @@
     </row>
     <row r="120" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="5"/>
-      <c r="B120" s="28"/>
-      <c r="C120" s="29"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="52"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -2476,8 +2477,8 @@
     </row>
     <row r="121" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="5"/>
-      <c r="B121" s="28"/>
-      <c r="C121" s="29"/>
+      <c r="B121" s="51"/>
+      <c r="C121" s="52"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -2487,8 +2488,8 @@
     </row>
     <row r="122" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="5"/>
-      <c r="B122" s="28"/>
-      <c r="C122" s="29"/>
+      <c r="B122" s="51"/>
+      <c r="C122" s="52"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -2498,8 +2499,8 @@
     </row>
     <row r="123" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="5"/>
-      <c r="B123" s="28"/>
-      <c r="C123" s="29"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="52"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -2509,8 +2510,8 @@
     </row>
     <row r="124" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5"/>
-      <c r="B124" s="28"/>
-      <c r="C124" s="29"/>
+      <c r="B124" s="51"/>
+      <c r="C124" s="52"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -2520,8 +2521,8 @@
     </row>
     <row r="125" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5"/>
-      <c r="B125" s="28"/>
-      <c r="C125" s="29"/>
+      <c r="B125" s="51"/>
+      <c r="C125" s="52"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -2531,8 +2532,8 @@
     </row>
     <row r="126" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5"/>
-      <c r="B126" s="28"/>
-      <c r="C126" s="29"/>
+      <c r="B126" s="51"/>
+      <c r="C126" s="52"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -2542,8 +2543,8 @@
     </row>
     <row r="127" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5"/>
-      <c r="B127" s="28"/>
-      <c r="C127" s="29"/>
+      <c r="B127" s="51"/>
+      <c r="C127" s="52"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -2553,8 +2554,8 @@
     </row>
     <row r="128" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5"/>
-      <c r="B128" s="28"/>
-      <c r="C128" s="29"/>
+      <c r="B128" s="51"/>
+      <c r="C128" s="52"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -2564,8 +2565,8 @@
     </row>
     <row r="129" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="5"/>
-      <c r="B129" s="28"/>
-      <c r="C129" s="29"/>
+      <c r="B129" s="51"/>
+      <c r="C129" s="52"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -2575,8 +2576,8 @@
     </row>
     <row r="130" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="5"/>
-      <c r="B130" s="28"/>
-      <c r="C130" s="29"/>
+      <c r="B130" s="51"/>
+      <c r="C130" s="52"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -2586,8 +2587,8 @@
     </row>
     <row r="131" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="5"/>
-      <c r="B131" s="28"/>
-      <c r="C131" s="29"/>
+      <c r="B131" s="51"/>
+      <c r="C131" s="52"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -2597,8 +2598,8 @@
     </row>
     <row r="132" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="5"/>
-      <c r="B132" s="28"/>
-      <c r="C132" s="29"/>
+      <c r="B132" s="51"/>
+      <c r="C132" s="52"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -2608,8 +2609,8 @@
     </row>
     <row r="133" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5"/>
-      <c r="B133" s="28"/>
-      <c r="C133" s="29"/>
+      <c r="B133" s="51"/>
+      <c r="C133" s="52"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -2619,8 +2620,8 @@
     </row>
     <row r="134" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="5"/>
-      <c r="B134" s="28"/>
-      <c r="C134" s="29"/>
+      <c r="B134" s="51"/>
+      <c r="C134" s="52"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -2630,8 +2631,8 @@
     </row>
     <row r="135" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="5"/>
-      <c r="B135" s="28"/>
-      <c r="C135" s="29"/>
+      <c r="B135" s="51"/>
+      <c r="C135" s="52"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -2641,8 +2642,8 @@
     </row>
     <row r="136" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="5"/>
-      <c r="B136" s="28"/>
-      <c r="C136" s="29"/>
+      <c r="B136" s="51"/>
+      <c r="C136" s="52"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -2652,8 +2653,8 @@
     </row>
     <row r="137" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="5"/>
-      <c r="B137" s="28"/>
-      <c r="C137" s="29"/>
+      <c r="B137" s="51"/>
+      <c r="C137" s="52"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -2663,8 +2664,8 @@
     </row>
     <row r="138" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="5"/>
-      <c r="B138" s="28"/>
-      <c r="C138" s="29"/>
+      <c r="B138" s="51"/>
+      <c r="C138" s="52"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -2674,8 +2675,8 @@
     </row>
     <row r="139" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="5"/>
-      <c r="B139" s="28"/>
-      <c r="C139" s="29"/>
+      <c r="B139" s="51"/>
+      <c r="C139" s="52"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
@@ -2685,8 +2686,8 @@
     </row>
     <row r="140" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="5"/>
-      <c r="B140" s="28"/>
-      <c r="C140" s="29"/>
+      <c r="B140" s="51"/>
+      <c r="C140" s="52"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -2696,8 +2697,8 @@
     </row>
     <row r="141" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="5"/>
-      <c r="B141" s="28"/>
-      <c r="C141" s="29"/>
+      <c r="B141" s="51"/>
+      <c r="C141" s="52"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -2707,8 +2708,8 @@
     </row>
     <row r="142" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="5"/>
-      <c r="B142" s="28"/>
-      <c r="C142" s="29"/>
+      <c r="B142" s="51"/>
+      <c r="C142" s="52"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -2718,8 +2719,8 @@
     </row>
     <row r="143" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="5"/>
-      <c r="B143" s="28"/>
-      <c r="C143" s="29"/>
+      <c r="B143" s="51"/>
+      <c r="C143" s="52"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -2729,8 +2730,8 @@
     </row>
     <row r="144" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="5"/>
-      <c r="B144" s="28"/>
-      <c r="C144" s="29"/>
+      <c r="B144" s="51"/>
+      <c r="C144" s="52"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -2740,8 +2741,8 @@
     </row>
     <row r="145" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="5"/>
-      <c r="B145" s="28"/>
-      <c r="C145" s="29"/>
+      <c r="B145" s="51"/>
+      <c r="C145" s="52"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -2751,8 +2752,8 @@
     </row>
     <row r="146" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="5"/>
-      <c r="B146" s="28"/>
-      <c r="C146" s="29"/>
+      <c r="B146" s="51"/>
+      <c r="C146" s="52"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -2762,8 +2763,8 @@
     </row>
     <row r="147" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="5"/>
-      <c r="B147" s="28"/>
-      <c r="C147" s="29"/>
+      <c r="B147" s="51"/>
+      <c r="C147" s="52"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -2773,8 +2774,8 @@
     </row>
     <row r="148" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="5"/>
-      <c r="B148" s="28"/>
-      <c r="C148" s="29"/>
+      <c r="B148" s="51"/>
+      <c r="C148" s="52"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -2784,8 +2785,8 @@
     </row>
     <row r="149" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="5"/>
-      <c r="B149" s="28"/>
-      <c r="C149" s="29"/>
+      <c r="B149" s="51"/>
+      <c r="C149" s="52"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -2795,8 +2796,8 @@
     </row>
     <row r="150" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="5"/>
-      <c r="B150" s="28"/>
-      <c r="C150" s="29"/>
+      <c r="B150" s="51"/>
+      <c r="C150" s="52"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -2806,26 +2807,126 @@
     </row>
   </sheetData>
   <mergeCells count="164">
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="H1:I2"/>
-    <mergeCell ref="D2:E3"/>
-    <mergeCell ref="H3:I4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
@@ -2850,126 +2951,26 @@
     <mergeCell ref="B129:C129"/>
     <mergeCell ref="B130:C130"/>
     <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="H1:I2"/>
+    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="H3:I4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
